--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -600,7 +600,11 @@
           <t>SP-COP-ENG</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
@@ -697,7 +701,11 @@
           <t>SP-INJ-ENG</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
@@ -1356,7 +1364,11 @@
           <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Gnd fuel press + VSS</t>
@@ -1635,7 +1647,11 @@
           <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Gnd flex + MAP</t>
@@ -2480,7 +2496,11 @@
           <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>Gnd oil/clnt/temps</t>
@@ -2573,7 +2593,11 @@
           <t>SP-SW12-ENG</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
@@ -2773,7 +2797,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2961,7 +2985,11 @@
           <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Gnd IAT/TPS/coolant</t>
@@ -3569,7 +3597,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3666,7 +3694,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4066,7 +4094,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4729,7 +4757,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4931,7 +4959,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5323,7 +5351,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5614,7 +5642,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5895,7 +5923,11 @@
           <t>SP-CANH-LAM</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>CAN H to CAN-Lambda</t>
@@ -6000,7 +6032,11 @@
           <t>SP-CANL-LAM</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>CAN L to CAN-Lambda</t>
@@ -6107,7 +6143,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6493,7 +6529,11 @@
           <t>SP-LAM12-B</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
@@ -6590,7 +6630,11 @@
           <t>SP-SW12-ENG</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
@@ -6687,7 +6731,11 @@
           <t>SP-LAMG-B</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>CAN-Lambda ground</t>
@@ -6784,7 +6832,11 @@
           <t>SP-GNDOUT-B-ENG</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>Gnd charge temp</t>
@@ -6877,7 +6929,11 @@
           <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>Gnd coolant press</t>
@@ -6970,7 +7026,11 @@
           <t>SP-COP-ENG</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
@@ -7067,7 +7127,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>Coil 1 ground</t>
@@ -7160,7 +7224,11 @@
           <t>SP-COP-ENG</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
@@ -7257,7 +7325,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>Coil 2 ground</t>
@@ -7350,7 +7422,11 @@
           <t>SP-COP-ENG</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
@@ -7447,7 +7523,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>Coil 3 ground</t>
@@ -7540,7 +7620,11 @@
           <t>SP-COP-ENG</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
@@ -7637,7 +7721,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>Coil 4 ground</t>
@@ -7730,7 +7818,11 @@
           <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>Gnd coolant temp</t>
@@ -7813,13 +7905,21 @@
           <t>ENG-GND-RING</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>Coil ground</t>
@@ -7912,7 +8012,11 @@
           <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>Gnd throttle sensor</t>
@@ -8013,7 +8117,11 @@
           <t>SP-SW12-ENG</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
@@ -8118,7 +8226,11 @@
           <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>Gnd flex fuel</t>
@@ -8219,7 +8331,11 @@
           <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>Gnd fuel pressure</t>
@@ -8312,7 +8428,11 @@
           <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>Gnd intake temp</t>
@@ -8405,7 +8525,11 @@
           <t>SP-INJ-ENG</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
@@ -8502,7 +8626,11 @@
           <t>SP-INJ-ENG</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
@@ -8599,7 +8727,11 @@
           <t>SP-INJ-ENG</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
@@ -8696,7 +8828,11 @@
           <t>SP-INJ-ENG</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
@@ -8793,7 +8929,11 @@
           <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>Gnd MAP sensor</t>
@@ -8886,7 +9026,11 @@
           <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>Gnd oil pressure</t>
@@ -8979,7 +9123,11 @@
           <t>SP-GNDOUT-B-ENG</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>Gnd oil temp</t>
@@ -9072,7 +9220,11 @@
           <t>STARTER-TRIGGER</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>Starter solenoid S</t>
@@ -9159,13 +9311,21 @@
           <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>SP-GNDOUT-B-ENG</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>Gnd oil/charge temp</t>
@@ -9248,7 +9408,11 @@
           <t>SP-LAM12-B</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>CAN-LAMBDA</t>
@@ -9345,7 +9509,11 @@
           <t>SP-LAMG-B</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>DRB102-ENGINE</t>
@@ -9448,7 +9616,11 @@
           <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>Gnd gearbox speed</t>
@@ -12990,7 +13162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -13034,12 +13206,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Contact PN 'solder splice' / 'solder onto the factory lead' = no contact; TBD = not confirmed by a maker document.</t>
+          <t>Pin 'Splice' / 'Terminal' / 'Screen' = an end with no cavity (a solder splice, a ring or spade lug, a cable screen).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>Contact PN 'solder splice' / 'solder onto the factory lead' = no contact; TBD = not confirmed by a maker document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Wires: 94   Connectors / ends: 54   Splices: 13   Spare cavities: 42</t>
         </is>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>795</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>852</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>765</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2615,7 +2615,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>827</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>827</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>827</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>827</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>827</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3423,7 +3423,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>827</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3535,7 +3535,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>827</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3995,7 +3995,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4779,7 +4779,7 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5011,7 +5011,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5463,7 +5463,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5807,7 +5807,7 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>262</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>109</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>293</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>510</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>427</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>105</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>322</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>217</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>234</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>136</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>291</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>115</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>410</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>394</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>275</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>107</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>42</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>156</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>484</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>715</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>795</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>501</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>501</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>867</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$99</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Splices'!$A$1:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -6135,7 +6135,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>DRB102-ENGINE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>293</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7556,7 +7556,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+        </is>
+      </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
@@ -7695,12 +7699,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>DRB102-ENGINE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7735,7 +7739,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7780,7 +7784,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+        </is>
+      </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
@@ -7919,12 +7927,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>DRB102-ENGINE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7959,7 +7967,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>105</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -8004,7 +8012,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+        </is>
+      </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
@@ -8067,7 +8079,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -8143,12 +8155,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>DRB102-ENGINE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8183,7 +8195,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -8228,7 +8240,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+        </is>
+      </c>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
@@ -10444,7 +10460,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>w_eng_gnd</t>
+          <t>w_cop_gnd_e_ae</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10459,12 +10475,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>DRB102-ENGINE</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10479,7 +10495,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Coil ground</t>
+          <t>Coil ground to the POWER box NEG bar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10489,22 +10505,22 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Yellow</t>
+          <t>Blue-White-Yellow-Yellow</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>795</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>M22759/16-10-0</t>
+          <t>M22759/16-12-0</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -10516,22 +10532,22 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0462-210-1231</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Coil ground splice - ignition coils 1-4 to the engine block ground stud</t>
+          <t>Coil ground splice - ignition coils 1-4 to bulkhead pin 4 (POWER box NEG bar)</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Engine block ground stud (RADLOK engine ground, H6), M6 ring</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>EGND</t>
+          <t>COPG</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10544,10 +10560,18 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="W89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+        </is>
+      </c>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>Dan 2026-10-29: coil ground straight to the glove-box POWER box NEG bar (cleanest return), not the engine block stud; 12 AWG like the COP feed (w_cop_pwr_e_ae, size-12 cavity 1); size-12 contact 12-14 AWG</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11693,7 +11717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12180,10 +12204,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -12900,7 +12924,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>STARTER-TRIGGER</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -12911,7 +12935,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Engine block ground stud (RADLOK engine ground, H6), M6 ring</t>
+          <t>Starter solenoid S (50) terminal post, spade</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -12931,28 +12955,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STARTER-TRIGGER</t>
+          <t>SP-CANH-LAM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Starter solenoid S (50) terminal post, spade</t>
+          <t>CAN H join - bulkhead, Lambda, 120 ohm end</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -12962,7 +12986,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SP-CANH-LAM</t>
+          <t>SP-CANL-LAM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -12973,7 +12997,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CAN H join - bulkhead, Lambda, 120 ohm end</t>
+          <t>CAN L join - bulkhead, Lambda, 120 ohm end</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -12993,7 +13017,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SP-CANL-LAM</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -13004,7 +13028,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CAN L join - bulkhead, Lambda, 120 ohm end</t>
+          <t>Coil ground splice - ignition coils 1-4 to bulkhead pin 4 (POWER box NEG bar)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -13014,7 +13038,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -13024,7 +13048,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -13035,7 +13059,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Coil ground splice - ignition coils 1-4 to the engine block ground stud</t>
+          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 15A) to coils 1-4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -13055,7 +13079,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -13066,7 +13090,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 15A) to coils 1-4</t>
+          <t>Sensor return splice - oil temp and charge temp, tied to the BH-B pin 29 splice</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -13076,7 +13100,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -13086,7 +13110,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG</t>
+          <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -13097,7 +13121,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sensor return splice - oil temp and charge temp, tied to the BH-B pin 29 splice</t>
+          <t>Sensor return splice - BH-B pin 29 (ECU B22) to oil and coolant pressure</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -13107,7 +13131,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -13117,7 +13141,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2</t>
+          <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -13128,7 +13152,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-B pin 29 (ECU B22) to oil and coolant pressure</t>
+          <t>Sensor return splice - BH-B pin 15 (ECU B22) to fuel pressure and gearbox speed</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -13138,7 +13162,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -13148,7 +13172,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG3</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -13159,17 +13183,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-B pin 15 (ECU B22) to fuel pressure and gearbox speed</t>
+          <t>Sensor return splice - BH-A pin 34 (ECU A24) to coolant temp, intake temp, throttle</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>crimp splice</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -13179,7 +13203,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
+          <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -13190,17 +13214,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-A pin 34 (ECU A24) to coolant temp, intake temp, throttle</t>
+          <t>Sensor return splice - BH-A pin 18 (ECU A24) to MAP and flex sensor</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>crimp splice</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -13210,7 +13234,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG2</t>
+          <t>SP-INJ-ENG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -13221,7 +13245,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-A pin 18 (ECU A24) to MAP and flex sensor</t>
+          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 15A) to injectors 1-4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -13231,7 +13255,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -13241,7 +13265,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SP-INJ-ENG</t>
+          <t>SP-LAM12-B</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -13252,7 +13276,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 15A) to injectors 1-4</t>
+          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 20 AWG lead</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -13262,7 +13286,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -13272,7 +13296,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SP-LAM12-B</t>
+          <t>SP-LAMG-B</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -13283,7 +13307,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 20 AWG lead</t>
+          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 20 AWG lead</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -13303,7 +13327,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SP-LAMG-B</t>
+          <t>SP-SW12-ENG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -13314,7 +13338,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 20 AWG lead</t>
+          <t>Switched +12 V splice - BH-A pin 30 to boost solenoid and flex sensor</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -13324,7 +13348,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -13334,73 +13358,69 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SP-SW12-ENG</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>R-TERM-END</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>120R 1/4W</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>resistor</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Switched +12 V splice - BH-A pin 30 to boost solenoid and flex sensor</t>
+          <t>r_term_end</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>solder splice</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>component lead 1 / 2 (as drawn)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R-TERM-END</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>120R 1/4W</t>
-        </is>
-      </c>
+          <t>CAB-CAM</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>resistor</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>r_term_end</t>
+          <t>cab_cam screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>component lead 1 / 2 (as drawn)</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CAB-CAM</t>
+          <t>CAB-CAN-LAM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -13411,7 +13431,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>cab_cam screen (floats at the device end)</t>
+          <t>cab_can_lam screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -13427,7 +13447,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CAB-CAN-LAM</t>
+          <t>CAB-CRANK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -13438,7 +13458,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>cab_can_lam screen (floats at the device end)</t>
+          <t>cab_crank screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -13454,7 +13474,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CAB-CRANK</t>
+          <t>CAB-ETBM-AE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -13465,7 +13485,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>cab_crank screen (floats at the device end)</t>
+          <t>cab_etbm_ae screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -13481,7 +13501,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CAB-ETBM-AE</t>
+          <t>CAB-ETBS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -13492,7 +13512,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>cab_etbm_ae screen (floats at the device end)</t>
+          <t>cab_etbs screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -13508,7 +13528,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CAB-ETBS</t>
+          <t>CAB-FLEX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -13519,7 +13539,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>cab_etbs screen (floats at the device end)</t>
+          <t>cab_flex screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -13535,7 +13555,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CAB-FLEX</t>
+          <t>CAB-KNOCK1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -13546,7 +13566,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>cab_flex screen (floats at the device end)</t>
+          <t>cab_knock1 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -13562,7 +13582,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CAB-KNOCK1</t>
+          <t>CAB-TURBO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -13573,7 +13593,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>cab_knock1 screen (floats at the device end)</t>
+          <t>cab_turbo screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -13589,7 +13609,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CAB-TURBO</t>
+          <t>CAB-VSS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -13600,7 +13620,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>cab_turbo screen (floats at the device end)</t>
+          <t>cab_vss screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -13613,35 +13633,8 @@
       </c>
       <c r="I54" t="inlineStr"/>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>CAB-VSS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>cable screen</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>cab_vss screen (floats at the device end)</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I55"/>
+  <autoFilter ref="A1:I54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13874,12 +13867,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>w_eng_gnd</t>
+          <t>w_cop_gnd_e_ae</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Coil ground splice - ignition coils 1-4 to the engine block ground stud</t>
+          <t>Coil ground splice - ignition coils 1-4 to bulkhead pin 4 (POWER box NEG bar)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -13891,11 +13884,11 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>8.550000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>w_cop1g (18 AWG), w_cop2g (18 AWG), w_cop3g (18 AWG), w_cop4g (18 AWG), w_eng_gnd (10 AWG)</t>
+          <t>w_cop1g (18 AWG), w_cop2g (18 AWG), w_cop3g (18 AWG), w_cop4g (18 AWG), w_cop_gnd_e_ae (12 AWG)</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14269,7 +14262,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14291,7 +14284,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14313,7 +14306,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14335,7 +14328,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14357,12 +14350,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0413-214-1205</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -14379,7 +14372,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14401,7 +14394,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14423,7 +14416,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14445,7 +14438,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14467,7 +14460,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14489,7 +14482,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -14511,7 +14504,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -14533,12 +14526,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -14555,12 +14548,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -14577,7 +14570,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -14599,12 +14592,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -14621,12 +14614,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -14643,7 +14636,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -14665,12 +14658,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -14687,12 +14680,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -14709,7 +14702,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -14731,7 +14724,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -14753,7 +14746,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -14775,7 +14768,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -14797,7 +14790,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -14819,7 +14812,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14841,7 +14834,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14863,7 +14856,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14885,7 +14878,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14907,7 +14900,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14929,12 +14922,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>0413-214-1205</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -14951,7 +14944,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14973,7 +14966,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -14995,7 +14988,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -15017,7 +15010,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -15039,7 +15032,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -15053,30 +15046,8 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>DRB102-ENGINE</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>0413-214-1205</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D42"/>
+  <autoFilter ref="A1:D41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15166,7 +15137,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wires: 98   Connectors / ends: 54   Splices: 13   Spare cavities: 41</t>
+          <t>Wires: 98   Connectors / ends: 53   Splices: 13   Spare cavities: 40</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$99</definedName>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6712,14 +6712,14 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>0462-201-2031</t>
+          <t>0462-005-2031</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6828,14 +6828,14 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>0462-201-2031</t>
+          <t>0462-005-2031</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 20 AWG lead</t>
+          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 20 AWG lead</t>
+          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0462-201-2031</t>
+          <t>0462-005-2031, 0462-201-2031</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 20 AWG lead</t>
+          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 20 AWG lead</t>
+          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 20 AWG lead</t>
+          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -14056,11 +14056,11 @@
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>3.83</v>
+        <v>4.62</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>w_lam12_be14 (12 AWG), w_lam12_be (20 AWG)</t>
+          <t>w_lam12_be14 (12 AWG), w_lam12_be (16 AWG)</t>
         </is>
       </c>
     </row>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 20 AWG lead</t>
+          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -14122,11 +14122,11 @@
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>3.83</v>
+        <v>4.62</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>w_lamg_be (20 AWG), w_lamg_be14 (12 AWG)</t>
+          <t>w_lamg_be (16 AWG), w_lamg_be14 (12 AWG)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -871,7 +871,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4779,7 +4779,7 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -6135,7 +6135,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>360</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>360</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>257</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>257</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>813</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>813</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2615,7 +2615,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3423,7 +3423,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3535,7 +3535,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3995,7 +3995,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4779,7 +4779,7 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5011,7 +5011,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5463,7 +5463,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5807,7 +5807,7 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6135,7 +6135,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>780</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -5260,7 +5260,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BDK 2.8</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5295,7 +5295,11 @@
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Knock plug contacts: Bosch BDK 2.8 with individual wire seals (Bosch Compact 1.1a catalog, 1 928 403 874; Dan 2026-10-29)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5376,7 +5380,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BDK 2.8</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5411,7 +5415,11 @@
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Knock plug contacts: Bosch BDK 2.8 with individual wire seals (Bosch Compact 1.1a catalog, 1 928 403 874; Dan 2026-10-29)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12590,7 +12598,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BDK 2.8</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -6259,7 +6259,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>855</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -6313,7 +6313,7 @@
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V | EHPS enable +12 V | owner proposed: longer half (drawn today as w_hv_mrs_en_e_ae on ECU-engine, 240 mm; w_hv_mrs_en_e on EngineRoom-C, 1460 mm)</t>
+          <t>EHPS enable +12 V | EHPS enable +12 V | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>855</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -6425,7 +6425,7 @@
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_mrs_e_ae on ECU-engine, 240 mm; w_mrs_e on EngineRoom-C, 1460 mm)</t>
+          <t>ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>855</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -6537,7 +6537,7 @@
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_eps_rly_ae on ECU-engine, 240 mm; w_eps_rly_e on EngineRoom-C, 1460 mm)</t>
+          <t>ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -6158,7 +6158,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4495,7 +4495,11 @@
       </c>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4576,7 +4580,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4611,7 +4615,11 @@
       </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4692,7 +4700,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4727,7 +4735,11 @@
       </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -11833,7 +11845,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>DT06-3S-CE05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11846,10 +11858,14 @@
           <t>Cam Hall Sensor (RacerX)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>W3S</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -11860,7 +11876,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Deutsch DT / DTM cavity numbers (moulded on the housing)</t>
         </is>
       </c>
     </row>
@@ -13197,7 +13213,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>crimp splice</t>
+          <t>D-436-37</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -13819,7 +13835,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>crimp splice</t>
+          <t>D-436-37</t>
         </is>
       </c>
       <c r="E5" t="n">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$99</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Splices'!$A$1:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -651,7 +651,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>813</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>813</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2615,7 +2615,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3423,7 +3423,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3535,7 +3535,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3995,7 +3995,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4779,7 +4779,7 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5011,7 +5011,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BDK 2.8</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5295,7 +5295,11 @@
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Knock plug contacts: Bosch BDK 2.8 with individual wire seals (Bosch Compact 1.1a catalog, 1 928 403 874; Dan 2026-10-29)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5351,7 +5355,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5376,7 +5380,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BDK 2.8</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5411,7 +5415,11 @@
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Knock plug contacts: Bosch BDK 2.8 with individual wire seals (Bosch Compact 1.1a catalog, 1 928 403 874; Dan 2026-10-29)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5463,7 +5471,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5579,7 +5587,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5695,7 +5703,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5807,7 +5815,7 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5923,7 +5931,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6031,7 +6039,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6135,7 +6143,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -6150,7 +6158,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6251,7 +6259,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>855</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6288,7 +6296,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -6305,7 +6313,7 @@
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V | EHPS enable +12 V | owner proposed: longer half (drawn today as w_hv_mrs_en_e_ae on ECU-engine, 240 mm; w_hv_mrs_en_e on EngineRoom-C, 1460 mm)</t>
+          <t>EHPS enable +12 V | EHPS enable +12 V | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6371,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>855</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6400,7 +6408,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -6417,7 +6425,7 @@
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_mrs_e_ae on ECU-engine, 240 mm; w_mrs_e on EngineRoom-C, 1460 mm)</t>
+          <t>ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6483,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>855</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6512,7 +6520,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -6529,7 +6537,7 @@
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_eps_rly_ae on ECU-engine, 240 mm; w_eps_rly_e on EngineRoom-C, 1460 mm)</t>
+          <t>ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7179,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -7471,12 +7479,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>DRB102-ENGINE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7511,7 +7519,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>293</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7556,7 +7564,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+        </is>
+      </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
@@ -7619,7 +7631,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>360</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7695,12 +7707,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>DRB102-ENGINE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7735,7 +7747,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>360</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7780,7 +7792,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+        </is>
+      </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
@@ -7843,7 +7859,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>257</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7919,12 +7935,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>DRB102-ENGINE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7959,7 +7975,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>257</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -8004,7 +8020,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+        </is>
+      </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
@@ -8067,7 +8087,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -8143,12 +8163,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>DRB102-ENGINE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8183,7 +8203,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -8228,7 +8248,11 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+        </is>
+      </c>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
@@ -10131,7 +10155,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -10251,7 +10275,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -10266,7 +10290,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10375,7 +10399,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -10390,7 +10414,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10444,7 +10468,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>w_eng_gnd</t>
+          <t>w_cop_gnd_e_ae</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10459,12 +10483,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>DRB102-ENGINE</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10479,7 +10503,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Coil ground</t>
+          <t>Coil ground to the POWER box NEG bar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10489,22 +10513,22 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Yellow</t>
+          <t>Blue-White-Yellow-Yellow</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>M22759/16-10-0</t>
+          <t>M22759/16-12-0</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -10516,22 +10540,22 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0462-210-1231</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Coil ground splice - ignition coils 1-4 to the engine block ground stud</t>
+          <t>Coil ground splice - ignition coils 1-4 to bulkhead pin 4 (POWER box NEG bar)</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Engine block ground stud (RADLOK engine ground, H6), M6 ring</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>EGND</t>
+          <t>COPG</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10544,10 +10568,18 @@
           <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
-      <c r="W89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+        </is>
+      </c>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>Dan 2026-10-29: coil ground straight to the glove-box POWER box NEG bar (cleanest return), not the engine block stud; 12 AWG like the COP feed (w_cop_pwr_e_ae, size-12 cavity 1); size-12 contact 12-14 AWG</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10607,7 +10639,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10723,7 +10755,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10943,7 +10975,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -11055,7 +11087,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -11167,7 +11199,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -11279,7 +11311,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>780</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -11395,7 +11427,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -11511,7 +11543,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -11623,7 +11655,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -11693,7 +11725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12180,10 +12212,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -12566,7 +12598,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BDK 2.8</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -12900,7 +12932,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ENG-GND-RING</t>
+          <t>STARTER-TRIGGER</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -12911,7 +12943,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Engine block ground stud (RADLOK engine ground, H6), M6 ring</t>
+          <t>Starter solenoid S (50) terminal post, spade</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -12931,28 +12963,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STARTER-TRIGGER</t>
+          <t>SP-CANH-LAM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Starter solenoid S (50) terminal post, spade</t>
+          <t>CAN H join - bulkhead, Lambda, 120 ohm end</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -12962,7 +12994,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SP-CANH-LAM</t>
+          <t>SP-CANL-LAM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -12973,7 +13005,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CAN H join - bulkhead, Lambda, 120 ohm end</t>
+          <t>CAN L join - bulkhead, Lambda, 120 ohm end</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -12993,7 +13025,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SP-CANL-LAM</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -13004,7 +13036,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CAN L join - bulkhead, Lambda, 120 ohm end</t>
+          <t>Coil ground splice - ignition coils 1-4 to bulkhead pin 4 (POWER box NEG bar)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -13014,7 +13046,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -13024,7 +13056,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -13035,7 +13067,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Coil ground splice - ignition coils 1-4 to the engine block ground stud</t>
+          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 15A) to coils 1-4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -13055,7 +13087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -13066,7 +13098,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 15A) to coils 1-4</t>
+          <t>Sensor return splice - oil temp and charge temp, tied to the BH-B pin 29 splice</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -13076,7 +13108,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -13086,7 +13118,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG</t>
+          <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -13097,7 +13129,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sensor return splice - oil temp and charge temp, tied to the BH-B pin 29 splice</t>
+          <t>Sensor return splice - BH-B pin 29 (ECU B22) to oil and coolant pressure</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -13107,7 +13139,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -13117,7 +13149,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2</t>
+          <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -13128,7 +13160,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-B pin 29 (ECU B22) to oil and coolant pressure</t>
+          <t>Sensor return splice - BH-B pin 15 (ECU B22) to fuel pressure and gearbox speed</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -13138,7 +13170,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -13148,7 +13180,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG3</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -13159,17 +13191,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-B pin 15 (ECU B22) to fuel pressure and gearbox speed</t>
+          <t>Sensor return splice - BH-A pin 34 (ECU A24) to coolant temp, intake temp, throttle</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>crimp splice</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -13179,7 +13211,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
+          <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -13190,17 +13222,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-A pin 34 (ECU A24) to coolant temp, intake temp, throttle</t>
+          <t>Sensor return splice - BH-A pin 18 (ECU A24) to MAP and flex sensor</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>crimp splice</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -13210,7 +13242,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG2</t>
+          <t>SP-INJ-ENG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -13221,7 +13253,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-A pin 18 (ECU A24) to MAP and flex sensor</t>
+          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 15A) to injectors 1-4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -13231,7 +13263,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -13241,7 +13273,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SP-INJ-ENG</t>
+          <t>SP-LAM12-B</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -13252,7 +13284,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 15A) to injectors 1-4</t>
+          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -13262,7 +13294,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -13272,7 +13304,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SP-LAM12-B</t>
+          <t>SP-LAMG-B</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -13283,7 +13315,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 16 AWG lead</t>
+          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -13303,7 +13335,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SP-LAMG-B</t>
+          <t>SP-SW12-ENG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -13314,7 +13346,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 16 AWG lead</t>
+          <t>Switched +12 V splice - BH-A pin 30 to boost solenoid and flex sensor</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -13324,7 +13356,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -13334,73 +13366,69 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SP-SW12-ENG</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>R-TERM-END</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>120R 1/4W</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>resistor</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Switched +12 V splice - BH-A pin 30 to boost solenoid and flex sensor</t>
+          <t>r_term_end</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>solder splice</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>component lead 1 / 2 (as drawn)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R-TERM-END</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>120R 1/4W</t>
-        </is>
-      </c>
+          <t>CAB-CAM</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>resistor</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>r_term_end</t>
+          <t>cab_cam screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>component lead 1 / 2 (as drawn)</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CAB-CAM</t>
+          <t>CAB-CAN-LAM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -13411,7 +13439,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>cab_cam screen (floats at the device end)</t>
+          <t>cab_can_lam screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -13427,7 +13455,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CAB-CAN-LAM</t>
+          <t>CAB-CRANK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -13438,7 +13466,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>cab_can_lam screen (floats at the device end)</t>
+          <t>cab_crank screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -13454,7 +13482,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CAB-CRANK</t>
+          <t>CAB-ETBM-AE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -13465,7 +13493,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>cab_crank screen (floats at the device end)</t>
+          <t>cab_etbm_ae screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -13481,7 +13509,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CAB-ETBM-AE</t>
+          <t>CAB-ETBS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -13492,7 +13520,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>cab_etbm_ae screen (floats at the device end)</t>
+          <t>cab_etbs screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -13508,7 +13536,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CAB-ETBS</t>
+          <t>CAB-FLEX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -13519,7 +13547,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>cab_etbs screen (floats at the device end)</t>
+          <t>cab_flex screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -13535,7 +13563,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CAB-FLEX</t>
+          <t>CAB-KNOCK1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -13546,7 +13574,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>cab_flex screen (floats at the device end)</t>
+          <t>cab_knock1 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -13562,7 +13590,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CAB-KNOCK1</t>
+          <t>CAB-TURBO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -13573,7 +13601,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>cab_knock1 screen (floats at the device end)</t>
+          <t>cab_turbo screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -13589,7 +13617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CAB-TURBO</t>
+          <t>CAB-VSS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -13600,7 +13628,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>cab_turbo screen (floats at the device end)</t>
+          <t>cab_vss screen (floats at the device end)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -13613,35 +13641,8 @@
       </c>
       <c r="I54" t="inlineStr"/>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>CAB-VSS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>cable screen</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>cab_vss screen (floats at the device end)</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I55"/>
+  <autoFilter ref="A1:I54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13874,12 +13875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>w_eng_gnd</t>
+          <t>w_cop_gnd_e_ae</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Coil ground splice - ignition coils 1-4 to the engine block ground stud</t>
+          <t>Coil ground splice - ignition coils 1-4 to bulkhead pin 4 (POWER box NEG bar)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -13891,11 +13892,11 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>8.550000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>w_cop1g (18 AWG), w_cop2g (18 AWG), w_cop3g (18 AWG), w_cop4g (18 AWG), w_eng_gnd (10 AWG)</t>
+          <t>w_cop1g (18 AWG), w_cop2g (18 AWG), w_cop3g (18 AWG), w_cop4g (18 AWG), w_cop_gnd_e_ae (12 AWG)</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14269,7 +14270,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14291,7 +14292,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14313,7 +14314,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14335,7 +14336,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14357,12 +14358,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0413-214-1205</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -14379,7 +14380,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14401,7 +14402,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14423,7 +14424,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14445,7 +14446,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14467,7 +14468,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14489,7 +14490,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -14511,7 +14512,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -14533,12 +14534,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -14555,12 +14556,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -14577,7 +14578,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -14599,12 +14600,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -14621,12 +14622,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -14643,7 +14644,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -14665,12 +14666,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -14687,12 +14688,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -14709,7 +14710,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -14731,7 +14732,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -14753,7 +14754,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -14775,7 +14776,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -14797,7 +14798,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -14819,7 +14820,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14841,7 +14842,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14863,7 +14864,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14885,7 +14886,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14907,7 +14908,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14929,12 +14930,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>0413-214-1205</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -14951,7 +14952,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14973,7 +14974,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -14995,7 +14996,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -15017,7 +15018,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -15039,7 +15040,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -15053,30 +15054,8 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>DRB102-ENGINE</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>0413-214-1205</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D42"/>
+  <autoFilter ref="A1:D41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15166,7 +15145,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wires: 98   Connectors / ends: 54   Splices: 13   Spare cavities: 41</t>
+          <t>Wires: 98   Connectors / ends: 53   Splices: 13   Spare cavities: 40</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -2032,7 +2032,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -4497,7 +4497,7 @@
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>device reference docs/devices/SENSOR-AND-ACTUATOR-REFERENCE.md (Coolant pressure pin table)</t>
+          <t>Dan's sensor sheet SENSORS_AND_COMPONENTS_MASTER (Ronybuy 150 psi): A GND, B supply, C output</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -2032,7 +2032,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4495,7 +4495,11 @@
       </c>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4576,7 +4580,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4611,7 +4615,11 @@
       </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4692,7 +4700,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4727,7 +4735,11 @@
       </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7246,7 +7258,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -11833,7 +11845,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>DT06-3S-CE05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11846,10 +11858,14 @@
           <t>Cam Hall Sensor (RacerX)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>W3S</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -11860,7 +11876,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Deutsch DT / DTM cavity numbers (moulded on the housing)</t>
         </is>
       </c>
     </row>
@@ -11981,7 +11997,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>device reference docs/devices/SENSOR-AND-ACTUATOR-REFERENCE.md (Coolant pressure pin table)</t>
+          <t>Dan's sensor sheet SENSORS_AND_COMPONENTS_MASTER (Ronybuy 150 psi): A GND, B supply, C output</t>
         </is>
       </c>
     </row>
@@ -13197,7 +13213,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>crimp splice</t>
+          <t>D-436-37</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -13819,7 +13835,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>crimp splice</t>
+          <t>D-436-37</t>
         </is>
       </c>
       <c r="E5" t="n">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$99</definedName>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>55A1821-18-2/0-9</t>
+          <t>55A1821-20-2/0-9</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>55A1821-18-2/0-9</t>
+          <t>55A1821-20-2/0-9</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>55A1821-18-2/0-9</t>
+          <t>55A1821-20-2/0-9</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -12302,7 +12302,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Bosch Motorsport ETB data sheet 51048715 (pins 1A-6F)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$99</definedName>
@@ -705,7 +705,7 @@
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Starter solenoid S | Starter S crosses the firewall on its own DRB102 size-12 cavity (Dan 2026-10-27); 12 AWG: the DRB size-12 contact takes 12-14 AWG, solenoid S draw is brief, OEM lead is lighter</t>
+          <t>Starter solenoid S Candidate plug: Toyota 1-way sealed 90980-11400 (4.8 mm TS187 female; Toyota RM1022E housing list), sold for Toyota starters with a 12-10 AWG terminal; tab width to be checked at the car (Needs Dan N67). | Starter S crosses the firewall on its own DRB102 size-12 cavity (Dan 2026-10-27); 12 AWG: the DRB size-12 contact takes 12-14 AWG, solenoid S draw is brief, OEM lead is lighter</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice onto the pigtail red lead</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice onto the pigtail green lead</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -5995,7 +5995,11 @@
       </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Housing 90980-11250 = 2.3 II mm female 2-way sealed (Toyota RM1022E housing list); plug kit owned (Ballenger BM-985510).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6103,7 +6107,11 @@
       </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Housing 90980-11250 = 2.3 II mm female 2-way sealed (Toyota RM1022E housing list); plug kit owned (Ballenger BM-985510).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7315,7 +7323,7 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice onto the pigtail black lead</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -11970,7 +11978,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>pigtail supplied with the sensor (owned)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -11986,7 +11994,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice onto the pigtail black lead, solder splice onto the pigtail green lead, solder splice onto the pigtail red lead</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -11997,7 +12005,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dan's sensor sheet SENSORS_AND_COMPONENTS_MASTER (Ronybuy 150 psi): A GND, B supply, C output</t>
+          <t>Dan's sensor sheet + seller connection guide (Dan 2026-10-30): A / plug 1 GND black, B / plug 2 supply red, C / plug 3 output green</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -4497,7 +4497,7 @@
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); leads 20 AWG x 1 m (ZF datasheet GS1005-GS1007, 2024-09-11), inside the DT pins' 16-20 AWG. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); leads 20 AWG x 1 m (ZF datasheet GS1005-GS1007, 2024-09-11), inside the DT pins' 16-20 AWG. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); leads 20 AWG x 1 m (ZF datasheet GS1005-GS1007, 2024-09-11), inside the DT pins' 16-20 AWG. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$99</definedName>
@@ -705,7 +705,7 @@
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Starter solenoid S | Starter S crosses the firewall on its own DRB102 size-12 cavity (Dan 2026-10-27); 12 AWG: the DRB size-12 contact takes 12-14 AWG, solenoid S draw is brief, OEM lead is lighter</t>
+          <t>Starter solenoid S Candidate plug: Toyota 1-way sealed 90980-11400 (4.8 mm TS187 female; Toyota RM1022E housing list), sold for Toyota starters with a 12-10 AWG terminal; tab width to be checked at the car (Needs Dan N67). | Starter S crosses the firewall on its own DRB102 size-12 cavity (Dan 2026-10-27); 12 AWG: the DRB size-12 contact takes 12-14 AWG, solenoid S draw is brief, OEM lead is lighter</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice onto the pigtail red lead</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice onto the pigtail green lead</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -4497,7 +4497,7 @@
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); leads 20 AWG x 1 m (ZF datasheet GS1005-GS1007, 2024-09-11), inside the DT pins' 16-20 AWG. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); leads 20 AWG x 1 m (ZF datasheet GS1005-GS1007, 2024-09-11), inside the DT pins' 16-20 AWG. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); lead gauge TBD. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
+          <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); leads 20 AWG x 1 m (ZF datasheet GS1005-GS1007, 2024-09-11), inside the DT pins' 16-20 AWG. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,11 @@
       </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Housing 90980-11250 = 2.3 II mm female 2-way sealed (Toyota RM1022E housing list); plug kit owned (Ballenger BM-985510).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6103,7 +6107,11 @@
       </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Housing 90980-11250 = 2.3 II mm female 2-way sealed (Toyota RM1022E housing list); plug kit owned (Ballenger BM-985510).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7315,7 +7323,7 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice onto the pigtail black lead</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -11970,7 +11978,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>pigtail supplied with the sensor (owned)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -11986,7 +11994,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice onto the pigtail black lead, solder splice onto the pigtail green lead, solder splice onto the pigtail red lead</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -11997,7 +12005,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dan's sensor sheet SENSORS_AND_COMPONENTS_MASTER (Ronybuy 150 psi): A GND, B supply, C output</t>
+          <t>Dan's sensor sheet + seller connection guide (Dan 2026-10-30): A / plug 1 GND black, B / plug 2 supply red, C / plug 3 output green</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -620,7 +620,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -668,7 +668,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>in kit CONN-76058 (Sumitomo TS187 4.8 mm sealed female, 12-10 AWG)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Starter solenoid S (50) terminal post, spade</t>
+          <t>Starter solenoid S (50) terminal, 1-way plug</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -705,7 +705,7 @@
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Starter solenoid S Candidate plug: Toyota 1-way sealed 90980-11400 (4.8 mm TS187 female; Toyota RM1022E housing list), sold for Toyota starters with a 12-10 AWG terminal; tab width to be checked at the car (Needs Dan N67). | Starter S crosses the firewall on its own DRB102 size-12 cavity (Dan 2026-10-27); 12 AWG: the DRB size-12 contact takes 12-14 AWG, solenoid S draw is brief, OEM lead is lighter</t>
+          <t>Starter solenoid S Plug 90980-11400 (Dan 2026-10-30, N67 A); kit Ballenger CONN-76058 has the 12-10 AWG terminal and seal; check the tab is 4.8 mm when fitting. | Starter S crosses the firewall on its own DRB102 size-12 cavity (Dan 2026-10-27); 12 AWG: the DRB size-12 contact takes 12-14 AWG, solenoid S draw is brief, OEM lead is lighter</t>
         </is>
       </c>
     </row>
@@ -12874,12 +12874,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TURBO-SPD</t>
+          <t>STARTER-TRIGGER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DT06-3S-CE05</t>
+          <t>90980-11400</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12889,40 +12889,36 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Turbo Speed Sensor</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>W3S</t>
-        </is>
-      </c>
+          <t>Starter solenoid S (50) terminal, 1-way plug</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>in kit CONN-76058 (Sumitomo TS187 4.8 mm sealed female, 12-10 AWG)</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Deutsch DT / DTM cavity numbers (moulded on the housing)</t>
+          <t>single cavity (Toyota RM1022E housing list: 90980-11400 is 1-way, 4.8 mm tab, sealed)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>TURBO-SPD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90980-11143</t>
+          <t>DT06-3S-CE05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12932,13 +12928,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>Turbo Speed Sensor</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>W3S</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -12949,40 +12949,48 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Toyota 3-wire speed sensor pinout (wilbo666 wiki; Daniel 2026-09-28)</t>
+          <t>Deutsch DT / DTM cavity numbers (moulded on the housing)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STARTER-TRIGGER</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>VSS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>90980-11143</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Starter solenoid S (50) terminal post, spade</t>
+          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Toyota 3-wire speed sensor pinout (wilbo666 wiki; Daniel 2026-09-28)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -815,7 +815,11 @@
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -888,7 +892,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -923,7 +927,11 @@
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -996,7 +1004,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1031,7 +1039,11 @@
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1104,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1139,7 +1151,11 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6296,7 +6312,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -6333,7 +6349,7 @@
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V | EHPS enable +12 V | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
+          <t>EHPS enable +12 V | EHPS enable +12 V Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); the harness wire splices to its lead. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6424,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -6445,7 +6461,7 @@
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
+          <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); the harness wire splices to its lead. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6536,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -6557,7 +6573,7 @@
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
+          <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); the harness wire splices to its lead. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -7435,7 +7451,7 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -7477,7 +7493,7 @@
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>Coil 1 +12 V | Coil 1 +12 V</t>
+          <t>Coil 1 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 1 +12 V</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7567,7 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -7591,7 +7607,11 @@
       </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7663,7 +7683,7 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -7705,7 +7725,7 @@
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>Coil 2 +12 V | Coil 2 +12 V</t>
+          <t>Coil 2 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 2 +12 V</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7799,7 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -7819,7 +7839,11 @@
       </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7891,7 +7915,7 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -7933,7 +7957,7 @@
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>Coil 3 +12 V | Coil 3 +12 V</t>
+          <t>Coil 3 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 3 +12 V</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8031,7 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -8047,7 +8071,11 @@
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8119,7 +8147,7 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -8161,7 +8189,7 @@
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>Coil 4 +12 V | Coil 4 +12 V</t>
+          <t>Coil 4 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 4 +12 V</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8263,7 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -8275,7 +8303,11 @@
       </c>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -12033,7 +12065,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -12072,7 +12104,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -12111,7 +12143,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -12150,7 +12182,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -12700,7 +12732,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -12739,7 +12771,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -12743,7 +12743,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MR-S (ZZW30) EWD power steering page (Dan 2026-10-30): P6 1 MH, 2 PGND; P7 1 IDUP, 2 SPD, 3 TC, 5 MRLY, 6 EFI, 7 TS; P8 1 IGB, 2 SIL, 4 WL</t>
         </is>
       </c>
     </row>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MR-S (ZZW30) EWD power steering page (Dan 2026-10-30): P6 1 MH, 2 PGND; P7 1 IDUP, 2 SPD, 3 TC, 5 MRLY, 6 EFI, 7 TS; P8 1 IGB, 2 SIL, 4 WL</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -620,7 +620,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -668,7 +668,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>in kit CONN-76058 (Sumitomo TS187 4.8 mm sealed female, 12-10 AWG)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Starter solenoid S (50) terminal post, spade</t>
+          <t>Starter solenoid S (50) terminal, 1-way plug</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -705,7 +705,7 @@
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Starter solenoid S Candidate plug: Toyota 1-way sealed 90980-11400 (4.8 mm TS187 female; Toyota RM1022E housing list), sold for Toyota starters with a 12-10 AWG terminal; tab width to be checked at the car (Needs Dan N67). | Starter S crosses the firewall on its own DRB102 size-12 cavity (Dan 2026-10-27); 12 AWG: the DRB size-12 contact takes 12-14 AWG, solenoid S draw is brief, OEM lead is lighter</t>
+          <t>Starter solenoid S Plug 90980-11400 (Dan 2026-10-30, N67 A); kit Ballenger CONN-76058 has the 12-10 AWG terminal and seal; check the tab is 4.8 mm when fitting. | Starter S crosses the firewall on its own DRB102 size-12 cavity (Dan 2026-10-27); 12 AWG: the DRB size-12 contact takes 12-14 AWG, solenoid S draw is brief, OEM lead is lighter</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -815,7 +815,11 @@
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -888,7 +892,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -923,7 +927,11 @@
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -996,7 +1004,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1031,7 +1039,11 @@
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1104,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1139,7 +1151,11 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6296,7 +6312,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -6333,7 +6349,7 @@
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V | EHPS enable +12 V | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
+          <t>EHPS enable +12 V | EHPS enable +12 V Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); the harness wire splices to its lead. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6424,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -6445,7 +6461,7 @@
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
+          <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); the harness wire splices to its lead. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6536,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -6557,7 +6573,7 @@
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
+          <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); the harness wire splices to its lead. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -7435,7 +7451,7 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -7477,7 +7493,7 @@
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>Coil 1 +12 V | Coil 1 +12 V</t>
+          <t>Coil 1 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 1 +12 V</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7567,7 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -7591,7 +7607,11 @@
       </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7663,7 +7683,7 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -7705,7 +7725,7 @@
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>Coil 2 +12 V | Coil 2 +12 V</t>
+          <t>Coil 2 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 2 +12 V</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7799,7 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -7819,7 +7839,11 @@
       </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7891,7 +7915,7 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -7933,7 +7957,7 @@
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>Coil 3 +12 V | Coil 3 +12 V</t>
+          <t>Coil 3 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 3 +12 V</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8031,7 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -8047,7 +8071,11 @@
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8119,7 +8147,7 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -8161,7 +8189,7 @@
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>Coil 4 +12 V | Coil 4 +12 V</t>
+          <t>Coil 4 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 4 +12 V</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8263,7 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -8275,7 +8303,11 @@
       </c>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -12033,7 +12065,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -12072,7 +12104,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -12111,7 +12143,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -12150,7 +12182,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -12700,7 +12732,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -12711,7 +12743,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MR-S (ZZW30) EWD power steering page (Dan 2026-10-30): P6 1 MH, 2 PGND; P7 1 IDUP, 2 SPD, 3 TC, 5 MRLY, 6 EFI, 7 TS; P8 1 IGB, 2 SIL, 4 WL</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12771,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -12750,7 +12782,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MR-S (ZZW30) EWD power steering page (Dan 2026-10-30): P6 1 MH, 2 PGND; P7 1 IDUP, 2 SPD, 3 TC, 5 MRLY, 6 EFI, 7 TS; P8 1 IGB, 2 SIL, 4 WL</t>
         </is>
       </c>
     </row>
@@ -12874,12 +12906,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TURBO-SPD</t>
+          <t>STARTER-TRIGGER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DT06-3S-CE05</t>
+          <t>90980-11400</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12889,40 +12921,36 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Turbo Speed Sensor</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>W3S</t>
-        </is>
-      </c>
+          <t>Starter solenoid S (50) terminal, 1-way plug</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>in kit CONN-76058 (Sumitomo TS187 4.8 mm sealed female, 12-10 AWG)</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Deutsch DT / DTM cavity numbers (moulded on the housing)</t>
+          <t>single cavity (Toyota RM1022E housing list: 90980-11400 is 1-way, 4.8 mm tab, sealed)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>TURBO-SPD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90980-11143</t>
+          <t>DT06-3S-CE05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12932,13 +12960,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>Turbo Speed Sensor</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>W3S</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -12949,40 +12981,48 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Toyota 3-wire speed sensor pinout (wilbo666 wiki; Daniel 2026-09-28)</t>
+          <t>Deutsch DT / DTM cavity numbers (moulded on the housing)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STARTER-TRIGGER</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>VSS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>90980-11143</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Starter solenoid S (50) terminal post, spade</t>
+          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Toyota 3-wire speed sensor pinout (wilbo666 wiki; Daniel 2026-09-28)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>55A1821-20-2/0-9</t>
+          <t>55A1821-16-2/0-9</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3265,7 +3265,7 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
+          <t>16 AWG core spliced to a short 20 AWG tail (M22759/16-20) at the ETB plug: the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>55A1821-20-2/0-9</t>
+          <t>55A1821-16-2/0-9</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
+          <t>16 AWG core spliced to a short 20 AWG tail (M22759/16-20) at the ETB plug: the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>55A1821-20-2/0-9</t>
+          <t>55A1821-16-2/0-9</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -3265,7 +3265,7 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16 AWG core spliced to a short 20 AWG tail (M22759/16-20) at the ETB plug: the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
+          <t>16 AWG core joined to a short (&lt;= 150 mm) 20 AWG tail (M22759/16-20) at the ETB plug with a TE Raychem D-436-37 sealed crimp splice (20-16 AWG each side, 150 C): the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16 AWG core spliced to a short 20 AWG tail (M22759/16-20) at the ETB plug: the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
+          <t>16 AWG core joined to a short (&lt;= 150 mm) 20 AWG tail (M22759/16-20) at the ETB plug with a TE Raychem D-436-37 sealed crimp splice (20-16 AWG each side, 150 C): the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>55A1821-20-2/0-9</t>
+          <t>55A1821-16-2/0-9</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3265,7 +3265,7 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
+          <t>16 AWG core joined to a short (&lt;= 150 mm) 20 AWG tail (M22759/16-20) at the ETB plug with a TE Raychem D-436-37 sealed crimp splice (20-16 AWG each side, 150 C): the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>55A1821-20-2/0-9</t>
+          <t>55A1821-16-2/0-9</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
+          <t>16 AWG core joined to a short (&lt;= 150 mm) 20 AWG tail (M22759/16-20) at the ETB plug with a TE Raychem D-436-37 sealed crimp splice (20-16 AWG each side, 150 C): the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>55A1821-20-2/0-9</t>
+          <t>55A1821-16-2/0-9</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -4903,7 +4903,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC MRS 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC MRS 5 A fuse</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>55A1821-16-2/0-9</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>in kit D 261 205 358-01</t>
+          <t>5-965906-1</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3265,7 +3265,7 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16 AWG core joined to a short (&lt;= 150 mm) 20 AWG tail (M22759/16-20) at the ETB plug with a TE Raychem D-436-37 sealed crimp splice (20-16 AWG each side, 150 C): the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
+          <t>18 AWG the whole circuit, no tail (Dan 2026-10-30, N77 A): TE MQS 0.63 sealed contact 5-965906-1 (20-18 AWG, 7.5 A) in place of the kit contact (24-20 AWG); TEST-FIT in the Bosch housing before building - no Bosch fit approval found. Fallback if it fails: 20 AWG whole circuit (kit contact, 55A1821-20 cable), ETB fuse 5 A. Motor ~2 A typical, &lt; 10 A max (Bosch data sheet). | owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>55A1821-16-2/0-9</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>in kit D 261 205 358-01</t>
+          <t>5-965906-1</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16 AWG core joined to a short (&lt;= 150 mm) 20 AWG tail (M22759/16-20) at the ETB plug with a TE Raychem D-436-37 sealed crimp splice (20-16 AWG each side, 150 C): the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
+          <t>18 AWG the whole circuit, no tail (Dan 2026-10-30, N77 A): TE MQS 0.63 sealed contact 5-965906-1 (20-18 AWG, 7.5 A) in place of the kit contact (24-20 AWG); TEST-FIT in the Bosch housing before building - no Bosch fit approval found. Fallback if it fails: 20 AWG whole circuit (kit contact, 55A1821-20 cable), ETB fuse 5 A. | owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>55A1821-16-2/0-9</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7883,7 +7883,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>Dan 2026-10-29: coil ground straight to the glove-box POWER box NEG bar (cleanest return), not the engine block stud; 12 AWG like the COP feed (w_cop_pwr_e_ae, size-12 cavity 1); size-12 contact 12-14 AWG</t>
+          <t>Dan 2026-10-29: coil ground straight to the glove-box POWER box NEG bar (cleanest return), not the engine block stud; 14 AWG like the COP feed (w_cop_pwr_e_ae, size-12 cavity 1) and the cabin half (Dan 2026-10-30, N74 A); size-12 contact 12-14 AWG</t>
         </is>
       </c>
     </row>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 15A) to coils 1-4</t>
+          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 10A) to coils 1-4</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10745,7 +10745,7 @@
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>Coil +12 V feed | Coil +12 V feed</t>
+          <t>Coil +12 V feed | Coil +12 V feed | 14 AWG like the cabin half (Dan 2026-10-30, N74 A): coils fire one at a time, ~8 A peak / ~4 A RMS for all 4 (Haltech 8 A per coil); COP fuse 10 A, capped by the 16 AWG branches (coil contact max 16 AWG)</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -11385,7 +11385,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 15A) to injectors 1-4</t>
+          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 7.5A) to injectors 1-4</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -11417,7 +11417,7 @@
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>Injector +12 V feed | Injector +12 V feed</t>
+          <t>Injector +12 V feed | Injector +12 V feed | 14 AWG like the cabin half (Dan 2026-10-30, N75 A): 4 x ~1.2 A (12 ohm high-impedance), INJ fuse 7.5 A</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12342,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>in kit D 261 205 358-01</t>
+          <t>5-965906-1, in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 15A) to coils 1-4</t>
+          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 10A) to coils 1-4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 15A) to injectors 1-4</t>
+          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 7.5A) to injectors 1-4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 15A) to injectors 1-4</t>
+          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 7.5A) to injectors 1-4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -13791,11 +13791,11 @@
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>8.550000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>w_inj_pwr_e_ae (12 AWG), w211 (16 AWG), w212 (16 AWG), w213 (16 AWG), w214 (16 AWG)</t>
+          <t>w_inj_pwr_e_ae (14 AWG), w211 (16 AWG), w212 (16 AWG), w213 (16 AWG), w214 (16 AWG)</t>
         </is>
       </c>
     </row>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 15A) to coils 1-4</t>
+          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 10A) to coils 1-4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -13824,11 +13824,11 @@
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>8.550000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>w_cop_pwr_e_ae (12 AWG), w112 (16 AWG), w113 (16 AWG), w114 (16 AWG), w115 (16 AWG)</t>
+          <t>w_cop_pwr_e_ae (14 AWG), w112 (16 AWG), w113 (16 AWG), w114 (16 AWG), w115 (16 AWG)</t>
         </is>
       </c>
     </row>
@@ -13956,11 +13956,11 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>6.6</v>
+        <v>7.32</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>w_cop1g (18 AWG), w_cop2g (18 AWG), w_cop3g (18 AWG), w_cop4g (18 AWG), w_cop_gnd_e_ae (12 AWG)</t>
+          <t>w_cop1g (16 AWG), w_cop2g (16 AWG), w_cop3g (16 AWG), w_cop4g (16 AWG), w_cop_gnd_e_ae (14 AWG)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>55A1821-16-2/0-9</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>in kit D 261 205 358-01</t>
+          <t>5-965906-1</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3265,7 +3265,7 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16 AWG core joined to a short (&lt;= 150 mm) 20 AWG tail (M22759/16-20) at the ETB plug with a TE Raychem D-436-37 sealed crimp splice (20-16 AWG each side, 150 C): the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
+          <t>18 AWG the whole circuit, no tail (Dan 2026-10-30, N77 A): TE MQS 0.63 sealed contact 5-965906-1 (20-18 AWG, 7.5 A) in place of the kit contact (24-20 AWG); TEST-FIT in the Bosch housing before building - no Bosch fit approval found. Fallback if it fails: 20 AWG whole circuit (kit contact, 55A1821-20 cable), ETB fuse 5 A. Motor ~2 A typical, &lt; 10 A max (Bosch data sheet). | owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>55A1821-16-2/0-9</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>in kit D 261 205 358-01</t>
+          <t>5-965906-1</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16 AWG core joined to a short (&lt;= 150 mm) 20 AWG tail (M22759/16-20) at the ETB plug with a TE Raychem D-436-37 sealed crimp splice (20-16 AWG each side, 150 C): the kit contact takes 24-20 AWG only (Dan 2026-10-30). | owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
+          <t>18 AWG the whole circuit, no tail (Dan 2026-10-30, N77 A): TE MQS 0.63 sealed contact 5-965906-1 (20-18 AWG, 7.5 A) in place of the kit contact (24-20 AWG); TEST-FIT in the Bosch housing before building - no Bosch fit approval found. Fallback if it fails: 20 AWG whole circuit (kit contact, 55A1821-20 cable), ETB fuse 5 A. | owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>55A1821-16-2/0-9</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC MRS 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC MRS 5 A fuse</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7883,7 +7883,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -10629,7 +10629,7 @@
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>Dan 2026-10-29: coil ground straight to the glove-box POWER box NEG bar (cleanest return), not the engine block stud; 12 AWG like the COP feed (w_cop_pwr_e_ae, size-12 cavity 1); size-12 contact 12-14 AWG</t>
+          <t>Dan 2026-10-29: coil ground straight to the glove-box POWER box NEG bar (cleanest return), not the engine block stud; 14 AWG like the COP feed (w_cop_pwr_e_ae, size-12 cavity 1) and the cabin half (Dan 2026-10-30, N74 A); size-12 contact 12-14 AWG</t>
         </is>
       </c>
     </row>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 15A) to coils 1-4</t>
+          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 10A) to coils 1-4</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10745,7 +10745,7 @@
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>Coil +12 V feed | Coil +12 V feed</t>
+          <t>Coil +12 V feed | Coil +12 V feed | 14 AWG like the cabin half (Dan 2026-10-30, N74 A): coils fire one at a time, ~8 A peak / ~4 A RMS for all 4 (Haltech 8 A per coil); COP fuse 10 A, capped by the 16 AWG branches (coil contact max 16 AWG)</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -11385,7 +11385,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 15A) to injectors 1-4</t>
+          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 7.5A) to injectors 1-4</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -11417,7 +11417,7 @@
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>Injector +12 V feed | Injector +12 V feed</t>
+          <t>Injector +12 V feed | Injector +12 V feed | 14 AWG like the cabin half (Dan 2026-10-30, N75 A): 4 x ~1.2 A (12 ohm high-impedance), INJ fuse 7.5 A</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -12342,7 +12342,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>in kit D 261 205 358-01</t>
+          <t>5-965906-1, in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 15A) to coils 1-4</t>
+          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 10A) to coils 1-4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 15A) to injectors 1-4</t>
+          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 7.5A) to injectors 1-4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 15A) to injectors 1-4</t>
+          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 7.5A) to injectors 1-4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -13791,11 +13791,11 @@
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>8.550000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>w_inj_pwr_e_ae (12 AWG), w211 (16 AWG), w212 (16 AWG), w213 (16 AWG), w214 (16 AWG)</t>
+          <t>w_inj_pwr_e_ae (14 AWG), w211 (16 AWG), w212 (16 AWG), w213 (16 AWG), w214 (16 AWG)</t>
         </is>
       </c>
     </row>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 15A) to coils 1-4</t>
+          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 10A) to coils 1-4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -13824,11 +13824,11 @@
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>8.550000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>w_cop_pwr_e_ae (12 AWG), w112 (16 AWG), w113 (16 AWG), w114 (16 AWG), w115 (16 AWG)</t>
+          <t>w_cop_pwr_e_ae (14 AWG), w112 (16 AWG), w113 (16 AWG), w114 (16 AWG), w115 (16 AWG)</t>
         </is>
       </c>
     </row>
@@ -13956,11 +13956,11 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>6.6</v>
+        <v>7.32</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>w_cop1g (18 AWG), w_cop2g (18 AWG), w_cop3g (18 AWG), w_cop4g (18 AWG), w_cop_gnd_e_ae (12 AWG)</t>
+          <t>w_cop1g (16 AWG), w_cop2g (16 AWG), w_cop3g (16 AWG), w_cop4g (16 AWG), w_cop_gnd_e_ae (14 AWG)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -1664,7 +1664,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>in kit CONN-75800</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5675,7 +5675,11 @@
       </c>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Crank plug: Toyota 90980-10947 (Sumitomo 2-way TS, Ballenger kit CONN-75800, owned; Dan 2026-10-31) mates the sensor's own socket; which cavity is signal vs ground is TBD (EWD)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5756,7 +5760,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>in kit CONN-75800</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5791,7 +5795,11 @@
       </c>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Crank plug: Toyota 90980-10947 (Sumitomo 2-way TS, Ballenger kit CONN-75800, owned; Dan 2026-10-31) mates the sensor's own socket; which cavity is signal vs ground is TBD (EWD)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9062,7 +9070,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -9072,14 +9080,14 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>12191819</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -9121,7 +9129,7 @@
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>Injector 1 +12 V | Injector 1 +12 V</t>
+          <t>Injector 1 +12 V | Injector 1 +12 V | Injector plugs: Ballenger CONN-76270 kits (black EV6/EV14 housing, GT 150 female 20-16 AWG, white cable seal 24-18 AWG), owned x4 (Dan 2026-10-31). Branches 18 AWG because the seal stops at 18 AWG (B12 step 2); load ~1.2 A each, INJ fuse 7.5 A.</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9186,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -9188,14 +9196,14 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>12191819</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -9294,7 +9302,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -9304,14 +9312,14 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>12191819</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -9410,7 +9418,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -9420,14 +9428,14 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>12191819</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -12205,7 +12213,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DT06-2S-CE05</t>
+          <t>90980-10947</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12218,14 +12226,10 @@
           <t>Crank VR Sensor (36-2)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>W2S</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>in kit CONN-75800</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -12236,7 +12240,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Deutsch DT / DTM cavity numbers (moulded on the housing)</t>
+          <t>TBD</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12486,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15419715</t>
+          <t>CONN-76270</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12498,7 +12502,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12191819, 15326426</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -12521,7 +12525,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15419715</t>
+          <t>CONN-76270</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -12537,7 +12541,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>12191819, 15326426</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -12560,7 +12564,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15419715</t>
+          <t>CONN-76270</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12576,7 +12580,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>12191819, 15326426</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -12599,7 +12603,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15419715</t>
+          <t>CONN-76270</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -12615,7 +12619,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>12191819, 15326426</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -13791,11 +13795,11 @@
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>7.32</v>
+        <v>5.37</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>w_inj_pwr_e_ae (14 AWG), w211 (16 AWG), w212 (16 AWG), w213 (16 AWG), w214 (16 AWG)</t>
+          <t>w_inj_pwr_e_ae (14 AWG), w211 (18 AWG), w212 (18 AWG), w213 (18 AWG), w214 (18 AWG)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -3265,7 +3265,7 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18 AWG the whole circuit, no tail (Dan 2026-10-30, N77 A): TE MQS 0.63 sealed contact 5-965906-1 (20-18 AWG, 7.5 A) in place of the kit contact (24-20 AWG); TEST-FIT in the Bosch housing before building - no Bosch fit approval found. Fallback if it fails: 20 AWG whole circuit (kit contact, 55A1821-20 cable), ETB fuse 5 A. Motor ~2 A typical, &lt; 10 A max (Bosch data sheet). | owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
+          <t>18 AWG the whole circuit, no tail (Dan 2026-10-30, N77 A): TE MQS 0.63 sealed contact 5-965906-1 (0.5-0.75 mm2, 20-18 AWG, 7.5 A) with green seal 1-967067-1 (insulation 1.4-2.1 mm): both on TE drawing C-967616 for housing 1-967616-1 (the Bosch 6-pin MQS plug); crimp pull-test one, 18 AWG is the top of the range. Motor ~2 A typical, &lt; 10 A max (Bosch data sheet). | owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18 AWG the whole circuit, no tail (Dan 2026-10-30, N77 A): TE MQS 0.63 sealed contact 5-965906-1 (20-18 AWG, 7.5 A) in place of the kit contact (24-20 AWG); TEST-FIT in the Bosch housing before building - no Bosch fit approval found. Fallback if it fails: 20 AWG whole circuit (kit contact, 55A1821-20 cable), ETB fuse 5 A. | owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
+          <t>18 AWG the whole circuit, no tail (Dan 2026-10-30, N77 A): TE MQS 0.63 sealed contact 5-965906-1 (0.5-0.75 mm2, 20-18 AWG, 7.5 A) with green seal 1-967067-1 (insulation 1.4-2.1 mm): both on TE drawing C-967616 for housing 1-967616-1 (the Bosch 6-pin MQS plug); crimp pull-test one, 18 AWG is the top of the range. | owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V | EHPS enable +12 V Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); the harness wire splices to its lead. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
+          <t>EHPS enable +12 V | EHPS enable +12 V Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); lead 2.0 mm2 (about 14 AWG, Toyota RM06H0E section F), larger than the harness wire, which solder-splices to it. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); the harness wire splices to its lead. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
+          <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); lead 2.0 mm2 (about 14 AWG, Toyota RM06H0E section F), larger than the harness wire, which solder-splices to it. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); the harness wire splices to its lead. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
+          <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); lead 2.0 mm2 (about 14 AWG, Toyota RM06H0E section F), larger than the harness wire, which solder-splices to it. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$99</definedName>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Y$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Splices'!$A$1:$G$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$41</definedName>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z99"/>
+  <dimension ref="A1:Y99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -446,23 +446,22 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="38" customWidth="1" min="17" max="17"/>
     <col width="38" customWidth="1" min="18" max="18"/>
-    <col width="38" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="50" customWidth="1" min="23" max="23"/>
-    <col width="34" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="60" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="50" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="60" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,85 +512,80 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Ident bands</t>
+          <t>Gauge (AWG)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Gauge (AWG)</t>
+          <t>Length (mm)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Length (mm)</t>
+          <t>Wire Type</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Wire Type</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Cable Part Number</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Cable Part Number</t>
+          <t>From Contact PN</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>From Contact PN</t>
+          <t>To Contact PN</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>To Contact PN</t>
+          <t>From Device</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>From Device</t>
+          <t>To Device</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>To Device</t>
+          <t>Circuit</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Circuit</t>
+          <t>Built With</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Built With</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Continues</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Continues</t>
+          <t>Route Branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Route Branch</t>
+          <t>OEM Ref</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>OEM Ref</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -641,69 +635,64 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>White-Yellow</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
           <t>M22759/16-12-2</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0462-210-1231</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0462-210-1231</t>
+          <t>in kit CONN-76058 (Sumitomo TS187 4.8 mm sealed female, 12-10 AWG)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>in kit CONN-76058 (Sumitomo TS187 4.8 mm sealed female, 12-10 AWG)</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Starter solenoid S (50) terminal, 1-way plug</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Starter solenoid S (50) terminal, 1-way plug</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_strl_c at DRB102-CABIN 3, to RB4 4</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Starter solenoid S Plug 90980-11400 (Dan 2026-10-30, N67 A); kit Ballenger CONN-76058 has the 12-10 AWG terminal and seal; check the tab is 4.8 mm when fitting. | Starter S crosses the firewall on its own DRB102 size-12 cavity (Dan 2026-10-27); 12 AWG: the DRB size-12 contact takes 12-14 AWG, solenoid S draw is brief, OEM lead is lighter</t>
         </is>
@@ -753,69 +742,64 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>White-Yellow-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>COP 1 (1ZZ)</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>COP 1 (1ZZ)</t>
+          <t>COP1</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>COP1</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>COP1</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w120_c at DRB102-CABIN 9, to ECU-A 13</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
@@ -865,69 +849,64 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>White-Yellow-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>COP 2 (1ZZ)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>COP 2 (1ZZ)</t>
+          <t>COP2</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>COP2</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>COP2</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w121_c at DRB102-CABIN 10, to ECU-A 12</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
@@ -977,69 +956,64 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>White-White-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1255</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>COP 3 (1ZZ)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>COP 3 (1ZZ)</t>
+          <t>COP3</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>COP3</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>COP3</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w122_c at DRB102-CABIN 11, to ECU-A 11</t>
         </is>
       </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
@@ -1089,69 +1063,64 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>White-White-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>COP 4 (1ZZ)</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>COP 4 (1ZZ)</t>
+          <t>COP4</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>COP4</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>COP4</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w123_c at DRB102-CABIN 12, to ECU-A 10</t>
         </is>
       </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
@@ -1201,69 +1170,64 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
           <t>M22759/16-20-3</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit 354404</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>in kit 354404</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Fuel Pressure Sensor</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Fuel Pressure Sensor</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>5V</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5V</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_5v_brail_c46 at DRB102-CABIN 13, to BUS-5V 6</t>
         </is>
       </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>runs straight through (the IX-B-RAIL inline went with the A / B split)</t>
         </is>
@@ -1313,69 +1277,64 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit 354404</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>in kit 354404</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Fuel Pressure Sensor</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Fuel Pressure Sensor</t>
+          <t>FUELP</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>FUELP</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>FUELP</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w32_c at DRB102-CABIN 14, to ECU-B 16</t>
         </is>
       </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1421,69 +1380,64 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Yellow-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1226</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
           <t>M22759/16-20-3</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit 354404</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>in kit 354404</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>MAP Sensor</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>MAP Sensor</t>
+          <t>MAP</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>MAP</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>MAP</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_5v_a_c39 at DRB102-CABIN 16, to BUS-5V 3</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1529,69 +1483,64 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Yellow-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1226</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit 354404</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>in kit 354404</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>MAP Sensor</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>MAP Sensor</t>
+          <t>MAP</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>MAP</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>MAP</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w26_c at DRB102-CABIN 17, to ECU-A 17</t>
         </is>
       </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1637,69 +1586,64 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Blue-Blue-White-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>in kit CONN-76270</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Injector 1</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Injector 1</t>
+          <t>INJ1</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>INJ1</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>INJ1</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w108_c at DRB102-CABIN 21, to ECU-A 4</t>
         </is>
       </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1745,69 +1689,64 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Blue-Blue-White-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>968</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>in kit CONN-76270</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Injector 2</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Injector 2</t>
+          <t>INJ2</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>INJ2</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>INJ2</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w109_c at DRB102-CABIN 22, to ECU-A 3</t>
         </is>
       </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1853,69 +1792,64 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Blue-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>887</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>in kit CONN-76270</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Injector 3</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Injector 3</t>
+          <t>INJ3</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>INJ3</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>INJ3</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w110_c at DRB102-CABIN 23, to ECU-A 2</t>
         </is>
       </c>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1961,69 +1895,64 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Blue-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>822</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>822</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>in kit CONN-76270</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Injector 4</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Injector 4</t>
+          <t>INJ4</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>INJ4</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>INJ4</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w111_c at DRB102-CABIN 24, to ECU-A 1</t>
         </is>
       </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2069,69 +1998,64 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>813</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
           <t>M22759/16-20-3</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>solder splice onto the pigtail red lead</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>solder splice onto the pigtail red lead</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Coolant Pressure Sensor</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Coolant Pressure Sensor</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>5V</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>5V</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_5v_brail_c47 at DRB102-CABIN 25, to BUS-5V 7</t>
         </is>
       </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>runs straight through (the IX-B-RAIL inline went with the A / B split)</t>
         </is>
@@ -2181,69 +2105,64 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>White-Yellow-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>813</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>solder splice onto the pigtail green lead</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>solder splice onto the pigtail green lead</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Coolant Pressure Sensor</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Coolant Pressure Sensor</t>
+          <t>CLNTP</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>CLNTP</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>CLNTP</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w35_c at DRB102-CABIN 26, to ECU-B 23</t>
         </is>
       </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2289,69 +2208,64 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
           <t>M22759/16-20-3</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit 354404</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>in kit 354404</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Oil Pressure Sensor</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Oil Pressure Sensor</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>5V</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>5V</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_5v_brail_c45 at DRB102-CABIN 27, to BUS-5V 5</t>
         </is>
       </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>runs straight through (the IX-B-RAIL inline went with the A / B split)</t>
         </is>
@@ -2401,69 +2315,64 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit 354404</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>in kit 354404</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Oil Pressure Sensor</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Oil Pressure Sensor</t>
+          <t>OILP</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>OILP</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>OILP</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w29_c at DRB102-CABIN 28, to ECU-B 15</t>
         </is>
       </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2509,77 +2418,72 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-FLEX</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>CAB-FLEX</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>15326426</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Flex Fuel Sensor</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Flex Fuel Sensor</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
           <t>FLEX</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>FLEX</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w48_c at DRB102-CABIN 31, to ECU-A 31</t>
         </is>
       </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2623,71 +2527,66 @@
           <t>Shield</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Yellow-Yellow-Yellow</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1185</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-FLEX</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>CAB-FLEX</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>cab_flex screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>cab_flex screen (floats at the device end)</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>FLEX</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>FLEX</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_shc_flex at DRB102-CABIN 32, to splice SP-SHIELD-A</t>
         </is>
       </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
         </is>
@@ -2737,69 +2636,64 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>White-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>IAT Sensor (Manifold)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>IAT Sensor (Manifold)</t>
+          <t>IAT</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>IAT</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>IAT</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w202_c at DRB102-CABIN 33, to ECU-A 16</t>
         </is>
       </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2845,77 +2739,72 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Blue-Blue-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-ETBS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>CAB-ETBS</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>in kit D 261 205 358-01</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Bosch 74.5mm ETB</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Bosch 74.5mm ETB</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
           <t>ETBS</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>ETBS</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rail_sp_5v_c at DRB102-CABIN 41, to BUS-5V 2</t>
         </is>
       </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2961,77 +2850,72 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Blue-Blue-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-ETBS</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>CAB-ETBS</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>in kit D 261 205 358-01</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Bosch 74.5mm ETB</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Bosch 74.5mm ETB</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>ETBS</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>ETBS</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w128_c at DRB102-CABIN 42, to ECU-A 22</t>
         </is>
       </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3077,77 +2961,72 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Blue-Blue-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-ETBS</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>CAB-ETBS</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>in kit D 261 205 358-01</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Bosch 74.5mm ETB</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Bosch 74.5mm ETB</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
           <t>ETBS</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>ETBS</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w129_c at DRB102-CABIN 44, to ECU-A 33</t>
         </is>
       </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3193,77 +3072,72 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Blue-Yellow-White</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-ETBM-AE</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>CAB-ETBM-AE</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>55A1821-18-2/0-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>5-965906-1</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>5-965906-1</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Bosch 74.5mm ETB</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Bosch 74.5mm ETB</t>
+          <t>ETBM</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
           <t>ETBM</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>ETBM</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w124_c at DRB102-CABIN 45, to ECU-B 18</t>
         </is>
       </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>18 AWG the whole circuit, no tail (Dan 2026-10-30, N77 A): TE MQS 0.63 sealed contact 5-965906-1 (0.5-0.75 mm2, 20-18 AWG, 7.5 A) with green seal 1-967067-1 (insulation 1.4-2.1 mm): both on TE drawing C-967616 for housing 1-967616-1 (the Bosch 6-pin MQS plug); crimp pull-test one, 18 AWG is the top of the range. Motor ~2 A typical, &lt; 10 A max (Bosch data sheet). | owner proposed: longer half (drawn today as w124_e on ECU-engine, 340 mm; w124_e_ae on ECU-engine, 590 mm)</t>
         </is>
@@ -3313,77 +3187,72 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Blue-Yellow-White</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-ETBM-AE</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>CAB-ETBM-AE</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>55A1821-18-2/0-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>5-965906-1</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>5-965906-1</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Bosch 74.5mm ETB</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Bosch 74.5mm ETB</t>
+          <t>ETBM</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
           <t>ETBM</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>ETBM</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w215_c at DRB102-CABIN 46, to ECU-B 26</t>
         </is>
       </c>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>18 AWG the whole circuit, no tail (Dan 2026-10-30, N77 A): TE MQS 0.63 sealed contact 5-965906-1 (0.5-0.75 mm2, 20-18 AWG, 7.5 A) with green seal 1-967067-1 (insulation 1.4-2.1 mm): both on TE drawing C-967616 for housing 1-967616-1 (the Bosch 6-pin MQS plug); crimp pull-test one, 18 AWG is the top of the range. | owner proposed: longer half (drawn today as w215_e on ECU-engine, 340 mm; w215_e_ae on ECU-engine, 590 mm)</t>
         </is>
@@ -3431,71 +3300,66 @@
           <t>Shield</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Blue-Blue-White</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-ETBS</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>CAB-ETBS</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>cab_etbs screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>cab_etbs screen (floats at the device end)</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
           <t>ETBS</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>ETBS</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_shc_etbs at DRB102-CABIN 47, to splice SP-SHIELD-A</t>
         </is>
       </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
         </is>
@@ -3543,71 +3407,66 @@
           <t>Shield</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Blue-Yellow-White</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-ETBM-AE</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>CAB-ETBM-AE</t>
+          <t>55A1821-18-2/0-9</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>55A1821-18-2/0-9</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>cab_etbm_ae screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>cab_etbm_ae screen (floats at the device end)</t>
+          <t>ETBM</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
           <t>ETBM</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>ETBM</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_shc_etbm at DRB102-CABIN 50, to splice SP-SHIELD-B</t>
         </is>
       </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end; owner TBD: a half has no length estimate (drawn today as cab_etbm_be_sh on ECU-engine, 340 mm; cab_etbm_ae_sh on ECU-engine, ? mm)</t>
         </is>
@@ -3657,77 +3516,72 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Yellow-Blue-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-TURBO</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>CAB-TURBO</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Turbo Speed Sensor</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Turbo Speed Sensor</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
           <t>TURBO</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>TURBO</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_5v_a_c40 at DRB102-CABIN 52, to BUS-5V 4</t>
         </is>
       </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3773,77 +3627,72 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Yellow-Blue-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-TURBO</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>CAB-TURBO</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Turbo Speed Sensor</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Turbo Speed Sensor</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
           <t>TURBO</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>TURBO</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w16_c at DRB102-CABIN 53, to ECU-A 30</t>
         </is>
       </c>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3889,77 +3738,72 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Yellow-Blue-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-TURBO</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>CAB-TURBO</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Turbo Speed Sensor</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Turbo Speed Sensor</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
           <t>TURBO</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>TURBO</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_a_c43 at DRB102-CABIN 56, to BUS-GNDOUT-A 5</t>
         </is>
       </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4003,71 +3847,66 @@
           <t>Shield</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Yellow-Blue-White</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-TURBO</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>CAB-TURBO</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>cab_turbo screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>cab_turbo screen (floats at the device end)</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
           <t>TURBO</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>TURBO</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_shc_turbo at DRB102-CABIN 57, to splice SP-SHIELD-A</t>
         </is>
       </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
         </is>
@@ -4117,69 +3956,64 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1156</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>12084200</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>12084200</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Boost Control Solenoid</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Boost Control Solenoid</t>
+          <t>BOOST</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
           <t>BOOST</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>BOOST</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w103_c at DRB102-CABIN 58, to ECU-A 21</t>
         </is>
       </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4225,69 +4059,64 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>White-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1483</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Charge-Pipe IAT Sensor</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Charge-Pipe IAT Sensor</t>
+          <t>CPIAT</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
           <t>CPIAT</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>CPIAT</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w204_c at DRB102-CABIN 59, to ECU-B 7</t>
         </is>
       </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4333,69 +4162,64 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1394</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Oil Temp Sensor</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Oil Temp Sensor</t>
+          <t>OILT</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
           <t>OILT</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>OILT</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w203_c at DRB102-CABIN 61, to ECU-B 6</t>
         </is>
       </c>
+      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4441,77 +4265,72 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>White-Blue-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>952</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-CAM</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>CAB-CAM</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Cam Hall Sensor (RacerX)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Cam Hall Sensor (RacerX)</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
           <t>8V</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>8V</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rail_sp_8v_c at DRB102-CABIN 63, to splice SP-8V</t>
         </is>
       </c>
+      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); leads 20 AWG x 1 m (ZF datasheet GS1005-GS1007, 2024-09-11), inside the DT pins' 16-20 AWG. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
@@ -4561,77 +4380,72 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>952</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-CAM</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>CAB-CAM</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Cam Hall Sensor (RacerX)</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Cam Hall Sensor (RacerX)</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
           <t>CAM</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>CAM</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_cam_sig_c at DRB102-CABIN 64, to splice SP-CAM</t>
         </is>
       </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); leads 20 AWG x 1 m (ZF datasheet GS1005-GS1007, 2024-09-11), inside the DT pins' 16-20 AWG. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
@@ -4681,77 +4495,72 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>952</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-CAM</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>CAB-CAM</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Cam Hall Sensor (RacerX)</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Cam Hall Sensor (RacerX)</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
           <t>CAM</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>CAM</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_a_c42 at DRB102-CABIN 65, to BUS-GNDOUT-A 4</t>
         </is>
       </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Sensor: Cherry (ZF) GS1007 hall from the Racer X cam kit, bare leads brown +V / black signal / blue ground (Dan sensor sheet); leads 20 AWG x 1 m (ZF datasheet GS1005-GS1007, 2024-09-11), inside the DT pins' 16-20 AWG. | Cam plug: harness side DT06-3S-CE05 + W3S + 0462-201-16141; the sensor's bare leads get DT04-3P + W3P + 0460-202-16141 (Dan 2026-10-29)</t>
         </is>
@@ -4799,71 +4608,66 @@
           <t>Shield</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Blue-Blue-Yellow</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-CAM</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>CAB-CAM</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>cab_cam screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>cab_cam screen (floats at the device end)</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
           <t>CAM</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>CAM</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_shc_cam at DRB102-CABIN 66, to splice SP-SHIELD-A</t>
         </is>
       </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
         </is>
@@ -4913,77 +4717,72 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-VSS</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>CAB-VSS</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
           <t>SW12</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>SW12</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rail_sw12_b_c_ac at DRB102-CABIN 67, to splice SP-SW12</t>
         </is>
       </c>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>+12 V gearbox speed | +12 V gearbox speed</t>
         </is>
@@ -5031,71 +4830,66 @@
           <t>Shield</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Yellow-White-Yellow</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-VSS</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>CAB-VSS</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>cab_vss screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>cab_vss screen (floats at the device end)</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
           <t>VSS</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>VSS</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_shc_vss at DRB102-CABIN 69, to splice SP-SHIELD-B</t>
         </is>
       </c>
+      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
         </is>
@@ -5145,69 +4939,64 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1128</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>ECT Sensor</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>ECT Sensor</t>
+          <t>ECT</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
           <t>ECT</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>ECT</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w201_c at DRB102-CABIN 70, to ECU-A 15</t>
         </is>
       </c>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5253,77 +5042,72 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Yellow-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>851</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-KNOCK1</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>CAB-KNOCK1</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>BDK 2.8</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>BDK 2.8</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Knock Sensor 1</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Knock Sensor 1</t>
+          <t>KNOCK1</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
           <t>KNOCK1</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>KNOCK1</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w205_c at DRB102-CABIN 71, to ECU-B 9</t>
         </is>
       </c>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Knock plug contacts: Bosch BDK 2.8 with individual wire seals (Bosch Compact 1.1a catalog, 1 928 403 874; Dan 2026-10-29)</t>
         </is>
@@ -5373,77 +5157,72 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Yellow-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>851</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-KNOCK1</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>CAB-KNOCK1</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>BDK 2.8</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>BDK 2.8</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Knock Sensor 1</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Knock Sensor 1</t>
+          <t>KNOCK1</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
           <t>KNOCK1</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>KNOCK1</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w12_c at DRB102-CABIN 72, to BUS-GNDOUT-B 6</t>
         </is>
       </c>
+      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Knock plug contacts: Bosch BDK 2.8 with individual wire seals (Bosch Compact 1.1a catalog, 1 928 403 874; Dan 2026-10-29)</t>
         </is>
@@ -5491,71 +5270,66 @@
           <t>Shield</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Yellow-Yellow</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-KNOCK1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>CAB-KNOCK1</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>cab_knock1 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>cab_knock1 screen (floats at the device end)</t>
+          <t>KNOCK1</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
           <t>KNOCK1</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>KNOCK1</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_shc_knock1 at DRB102-CABIN 73, to splice SP-SHIELD-B</t>
         </is>
       </c>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
         </is>
@@ -5605,77 +5379,72 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-CRANK</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>CAB-CRANK</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit CONN-75800</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>in kit CONN-75800</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Crank VR Sensor (36-2)</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Crank VR Sensor (36-2)</t>
+          <t>CRANK</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
           <t>CRANK</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>CRANK</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w200_c at DRB102-CABIN 74, to ECU-A 8</t>
         </is>
       </c>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>Crank plug: Toyota 90980-10947 (Sumitomo 2-way TS, Ballenger kit CONN-75800, owned; Dan 2026-10-31) mates the sensor's own socket; which cavity is signal vs ground is TBD (EWD)</t>
         </is>
@@ -5725,77 +5494,72 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-CRANK</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>CAB-CRANK</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>in kit CONN-75800</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>in kit CONN-75800</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Crank VR Sensor (36-2)</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Crank VR Sensor (36-2)</t>
+          <t>CRANK</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
           <t>CRANK</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>CRANK</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_a_c41 at DRB102-CABIN 75, to BUS-GNDOUT-A 3</t>
         </is>
       </c>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Crank plug: Toyota 90980-10947 (Sumitomo 2-way TS, Ballenger kit CONN-75800, owned; Dan 2026-10-31) mates the sensor's own socket; which cavity is signal vs ground is TBD (EWD)</t>
         </is>
@@ -5843,71 +5607,66 @@
           <t>Shield</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Yellow-Blue</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-CRANK</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>CAB-CRANK</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>cab_crank screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>cab_crank screen (floats at the device end)</t>
+          <t>CRANK</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
           <t>CRANK</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>CRANK</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_shc_crank at DRB102-CABIN 76, to splice SP-SHIELD-A</t>
         </is>
       </c>
+      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
         </is>
@@ -5957,69 +5716,64 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1454</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
           <t>M22759/16-16-2</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Back-up SW B1</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Back-up SW B1</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
           <t>REV</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>REV</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rev_feed_c at DRB102-CABIN 77, to IG2 4</t>
         </is>
       </c>
+      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Housing 90980-11250 = 2.3 II mm female 2-way sealed (Toyota RM1022E housing list); plug kit owned (Ballenger BM-985510).</t>
         </is>
@@ -6069,69 +5823,64 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1454</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
           <t>M22759/16-16-4</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Back-up SW B1</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Back-up SW B1</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
           <t>REV</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>REV</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rev_sw_c at DRB102-CABIN 78, to splice SP-REV</t>
         </is>
       </c>
+      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Housing 90980-11250 = 2.3 II mm female 2-way sealed (Toyota RM1022E housing list); plug kit owned (Ballenger BM-985510).</t>
         </is>
@@ -6179,71 +5928,66 @@
           <t>Shield</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-LAMCAN-BE</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>CAB-LAMCAN-BE</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>55A1821-20-9/5-9</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>cab_can_lam screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>cab_can_lam screen (floats at the device end)</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin cab_canbh_bc_sh at DRB102-CABIN 81, to splice SP-CAN-SH-BH</t>
         </is>
       </c>
+      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the CAN-Lambda end; owned by AB-engine (Dan 2026-10-27)</t>
         </is>
@@ -6293,69 +6037,64 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Blue-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>855</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
           <t>M22759/16-20-2</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>82998-12440</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>MR-S EHPS pump plug C</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>MR-S EHPS pump plug C</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
           <t>EPSEN</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>EPSEN</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_fb_mrs_en at DRB102-CABIN 83, to LOGIC BUS2-12</t>
         </is>
       </c>
+      <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>EHPS enable +12 V | EHPS enable +12 V Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); lead 2.0 mm2 (about 14 AWG, Toyota RM06H0E section F), larger than the harness wire, which solder-splices to it. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
@@ -6405,69 +6144,64 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>855</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>82998-12440</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>MR-S EHPS pump plug B</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>MR-S EHPS pump plug B</t>
+          <t>MRS</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
           <t>MRS</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>MRS</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_mrs_c at DRB102-CABIN 84, to ECU-A 27</t>
         </is>
       </c>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); lead 2.0 mm2 (about 14 AWG, Toyota RM06H0E section F), larger than the harness wire, which solder-splices to it. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
@@ -6517,69 +6251,64 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>855</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
           <t>M22759/16-18-9</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>82998-12440</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>82998-12440</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>MR-S EHPS pump plug B</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>MR-S EHPS pump plug B</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_eps_rly at DRB102-CABIN 85, to K-EPS 85</t>
         </is>
       </c>
+      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); lead 2.0 mm2 (about 14 AWG, Toyota RM06H0E section F), larger than the harness wire, which solder-splices to it. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
@@ -6633,69 +6362,64 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>262</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
           <t>M22759/16-20-2</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>12084200</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>12084200</t>
+          <t>solder splice SP-SW12-ENG</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>solder splice SP-SW12-ENG</t>
+          <t>Boost Control Solenoid</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Boost Control Solenoid</t>
+          <t>via SP-SW12-ENG</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>via SP-SW12-ENG</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-SW12-ENG</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SP-SW12-ENG</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rail_sp_sw12_c at DRB102-CABIN 30, to splice SP-SW12</t>
         </is>
       </c>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>+12 V boost sol | +12 V boost sol</t>
         </is>
@@ -6749,69 +6473,64 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Blue-White-White</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
           <t>M22759/16-16-2</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0462-005-2031</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>0462-005-2031</t>
+          <t>solder splice SP-LAM12-B</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>solder splice SP-LAM12-B</t>
+          <t>Link CAN-Lambda</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Link CAN-Lambda</t>
+          <t>via SP-LAM12-B</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>via SP-LAM12-B</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-LAM12-B</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>SP-LAM12-B</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_lam12_cp at DRB102-CABIN 95, to LOGIC BUS2-1</t>
         </is>
       </c>
+      <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner TBD: a half has no length estimate (drawn today as w_lam12_be on ECU-engine, ? mm; w_lam12_can on CAN, 140 mm)</t>
         </is>
@@ -6865,69 +6584,64 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Blue-White-White</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
           <t>M22759/16-16-0</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0462-005-2031</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>0462-005-2031</t>
+          <t>solder splice SP-LAMG-B</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>solder splice SP-LAMG-B</t>
+          <t>Link CAN-Lambda</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Link CAN-Lambda</t>
+          <t>via SP-LAMG-B</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>via SP-LAMG-B</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-LAMG-B</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>SP-LAMG-B</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_lamg_ac at DRB102-CABIN 96, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
+      <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>owner TBD: a half has no length estimate (drawn today as w_lamg_can on CAN, 140 mm; w_lamg_be on ECU-engine, ? mm)</t>
         </is>
@@ -6981,69 +6695,64 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
           <t>M22759/16-20-5</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0462-201-2031</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>0462-201-2031</t>
+          <t>solder splice SP-CANL-LAM</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>solder splice SP-CANL-LAM</t>
+          <t>Link CAN-Lambda</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Link CAN-Lambda</t>
+          <t>via SP-CANL-LAM</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>via SP-CANL-LAM</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-CANL-LAM</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>SP-CANL-LAM</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin wc_l_bh_bc at DRB102-CABIN 80, to splice SP-CANL</t>
         </is>
       </c>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Splice and 120R terminator sit in the heat-shrink right behind the CAN-Lambda plug; the shielded pair runs to it (Dan 2026-10-27; the Link CAN-Lambda has no internal terminator, manual 4.1)</t>
         </is>
@@ -7097,69 +6806,64 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
           <t>M22759/16-20-9</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0462-201-2031</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>0462-201-2031</t>
+          <t>solder splice SP-CANH-LAM</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>solder splice SP-CANH-LAM</t>
+          <t>Link CAN-Lambda</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Link CAN-Lambda</t>
+          <t>via SP-CANH-LAM</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>via SP-CANH-LAM</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-CANH-LAM</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SP-CANH-LAM</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin wc_h_bh_bc at DRB102-CABIN 79, to splice SP-CANH</t>
         </is>
       </c>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>Splice and 120R terminator sit in the heat-shrink right behind the CAN-Lambda plug; the shielded pair runs to it (Dan 2026-10-27; the Link CAN-Lambda has no internal terminator, manual 4.1)</t>
         </is>
@@ -7213,69 +6917,64 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>White-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>8100-0461</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>solder splice SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG</t>
+          <t>Charge-Pipe IAT Sensor</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Charge-Pipe IAT Sensor</t>
+          <t>via SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
+          <t>CPIAT</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>CPIAT</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_b_c19 at DRB102-CABIN 29, to BUS-GNDOUT-B 7</t>
         </is>
       </c>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7325,69 +7024,64 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>White-Yellow-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>solder splice onto the pigtail black lead</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>solder splice onto the pigtail black lead</t>
+          <t>solder splice SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG2</t>
+          <t>Coolant Pressure Sensor</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Coolant Pressure Sensor</t>
+          <t>via SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG2</t>
+          <t>CLNTP</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>CLNTP</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_b_c19 at DRB102-CABIN 29, to BUS-GNDOUT-B 7</t>
         </is>
       </c>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7437,69 +7131,64 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Blue-White-Yellow</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>293</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
           <t>M22759/16-16-2</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice SP-COP-ENG</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>solder splice SP-COP-ENG</t>
+          <t>COP 1 (1ZZ)</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>COP 1 (1ZZ)</t>
+          <t>via SP-COP-ENG</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>via SP-COP-ENG</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Coil 1 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 1 +12 V</t>
         </is>
@@ -7553,69 +7242,64 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>White-Yellow-Yellow</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>293</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
           <t>M22759/16-16-0</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>solder splice SP-CHASSIS-ENG</t>
+          <t>COP 1 (1ZZ)</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>COP 1 (1ZZ)</t>
+          <t>via SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>via SP-CHASSIS-ENG</t>
+          <t>COP1</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>COP1</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
+      <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
@@ -7669,69 +7353,64 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Blue-White-Yellow</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>360</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
           <t>M22759/16-16-2</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice SP-COP-ENG</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>solder splice SP-COP-ENG</t>
+          <t>COP 2 (1ZZ)</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>COP 2 (1ZZ)</t>
+          <t>via SP-COP-ENG</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>via SP-COP-ENG</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
+      <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Coil 2 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 2 +12 V</t>
         </is>
@@ -7785,69 +7464,64 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>White-Yellow-White</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>360</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
           <t>M22759/16-16-0</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>solder splice SP-CHASSIS-ENG</t>
+          <t>COP 2 (1ZZ)</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>COP 2 (1ZZ)</t>
+          <t>via SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>via SP-CHASSIS-ENG</t>
+          <t>COP2</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>COP2</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
+      <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
@@ -7901,69 +7575,64 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Blue-White-Yellow</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>257</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
           <t>M22759/16-16-2</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice SP-COP-ENG</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>solder splice SP-COP-ENG</t>
+          <t>COP 3 (1ZZ)</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>COP 3 (1ZZ)</t>
+          <t>via SP-COP-ENG</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>via SP-COP-ENG</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
+      <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>Coil 3 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 3 +12 V</t>
         </is>
@@ -8017,69 +7686,64 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>White-White-Yellow</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>257</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
           <t>M22759/16-16-0</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>solder splice SP-CHASSIS-ENG</t>
+          <t>COP 3 (1ZZ)</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>COP 3 (1ZZ)</t>
+          <t>via SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>via SP-CHASSIS-ENG</t>
+          <t>COP3</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>COP3</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
+      <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
@@ -8133,69 +7797,64 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Blue-White-Yellow</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>152</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
           <t>M22759/16-16-2</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice SP-COP-ENG</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>solder splice SP-COP-ENG</t>
+          <t>COP 4 (1ZZ)</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>COP 4 (1ZZ)</t>
+          <t>via SP-COP-ENG</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>via SP-COP-ENG</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
+      <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Coil 4 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 4 +12 V</t>
         </is>
@@ -8249,69 +7908,64 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>White-White-White</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>152</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
           <t>M22759/16-16-0</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>solder splice SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>solder splice SP-CHASSIS-ENG</t>
+          <t>COP 4 (1ZZ)</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>COP 4 (1ZZ)</t>
+          <t>via SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>via SP-CHASSIS-ENG</t>
+          <t>COP4</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>COP4</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
+      <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
@@ -8365,69 +8019,64 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>234</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>8100-0461</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>solder splice SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-ENG</t>
+          <t>ECT Sensor</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>ECT Sensor</t>
+          <t>via SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-ENG</t>
+          <t>ECT</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>ECT</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rail_sp_gndout_c at DRB102-CABIN 34, to BUS-GNDOUT-A 2</t>
         </is>
       </c>
+      <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8477,77 +8126,72 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Blue-Blue-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>136</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-ETBS</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>CAB-ETBS</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>in kit D 261 205 358-01</t>
+          <t>solder splice SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-ENG</t>
+          <t>Bosch 74.5mm ETB</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Bosch 74.5mm ETB</t>
+          <t>via SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-ENG</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>ETBS</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rail_sp_gndout_c at DRB102-CABIN 34, to BUS-GNDOUT-A 2</t>
         </is>
       </c>
+      <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8597,77 +8241,72 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>291</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-FLEX</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>CAB-FLEX</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>15326426</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>solder splice SP-SW12-ENG</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>solder splice SP-SW12-ENG</t>
+          <t>Flex Fuel Sensor</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Flex Fuel Sensor</t>
+          <t>via SP-SW12-ENG</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>via SP-SW12-ENG</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-SW12-ENG</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>SP-SW12-ENG</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rail_sp_sw12_c at DRB102-CABIN 30, to splice SP-SW12</t>
         </is>
       </c>
+      <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>+12 V flex fuel | +12 V flex fuel</t>
         </is>
@@ -8721,77 +8360,72 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>115</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-FLEX</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>CAB-FLEX</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>15326426</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>solder splice SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-ENG2</t>
+          <t>Flex Fuel Sensor</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Flex Fuel Sensor</t>
+          <t>via SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-ENG2</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG2</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_a_c44 at DRB102-CABIN 18, to BUS-GNDOUT-A 6</t>
         </is>
       </c>
+      <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8841,69 +8475,64 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>410</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>in kit 354404</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>in kit 354404</t>
+          <t>solder splice SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG3</t>
+          <t>Fuel Pressure Sensor</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Fuel Pressure Sensor</t>
+          <t>via SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG3</t>
+          <t>FUELP</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>FUELP</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG3</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_b_c21 at DRB102-CABIN 15, to BUS-GNDOUT-B 8</t>
         </is>
       </c>
+      <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8953,69 +8582,64 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>White-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>394</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>8100-0461</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>solder splice SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-ENG</t>
+          <t>IAT Sensor (Manifold)</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>IAT Sensor (Manifold)</t>
+          <t>via SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-ENG</t>
+          <t>IAT</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>IAT</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rail_sp_gndout_c at DRB102-CABIN 34, to BUS-GNDOUT-A 2</t>
         </is>
       </c>
+      <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9065,69 +8689,64 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Blue-White-Blue</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>275</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
           <t>M22759/16-18-2</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>in kit CONN-76270</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>in kit CONN-76270</t>
+          <t>solder splice SP-INJ-ENG</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>solder splice SP-INJ-ENG</t>
+          <t>Injector 1</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Injector 1</t>
+          <t>via SP-INJ-ENG</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>via SP-INJ-ENG</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-INJ-ENG</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>SP-INJ-ENG</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
+      <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>Injector 1 +12 V | Injector 1 +12 V | Injector plugs: Ballenger CONN-76270 kits (black EV6/EV14 housing, GT 150 female 20-16 AWG, white cable seal 24-18 AWG), owned x4 (Dan 2026-10-31). Branches 18 AWG because the seal stops at 18 AWG (B12 step 2); load ~1.2 A each, INJ fuse 7.5 A.</t>
         </is>
@@ -9181,69 +8800,64 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Blue-White-Blue</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>188</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
           <t>M22759/16-18-2</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>in kit CONN-76270</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>in kit CONN-76270</t>
+          <t>solder splice SP-INJ-ENG</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>solder splice SP-INJ-ENG</t>
+          <t>Injector 2</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Injector 2</t>
+          <t>via SP-INJ-ENG</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>via SP-INJ-ENG</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-INJ-ENG</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SP-INJ-ENG</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
+      <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>Injector 2 +12 V | Injector 2 +12 V</t>
         </is>
@@ -9297,69 +8911,64 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Blue-White-Blue</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>107</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
           <t>M22759/16-18-2</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>in kit CONN-76270</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>in kit CONN-76270</t>
+          <t>solder splice SP-INJ-ENG</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>solder splice SP-INJ-ENG</t>
+          <t>Injector 3</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Injector 3</t>
+          <t>via SP-INJ-ENG</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>via SP-INJ-ENG</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-INJ-ENG</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>SP-INJ-ENG</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
+      <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>Injector 3 +12 V | Injector 3 +12 V</t>
         </is>
@@ -9413,69 +9022,64 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Blue-White-Blue</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
           <t>M22759/16-18-2</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>in kit CONN-76270</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>in kit CONN-76270</t>
+          <t>solder splice SP-INJ-ENG</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>solder splice SP-INJ-ENG</t>
+          <t>Injector 4</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Injector 4</t>
+          <t>via SP-INJ-ENG</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>via SP-INJ-ENG</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-INJ-ENG</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>SP-INJ-ENG</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
+      <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>Injector 4 +12 V | Injector 4 +12 V</t>
         </is>
@@ -9529,69 +9133,64 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Yellow-White</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>156</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>in kit 354404</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>in kit 354404</t>
+          <t>solder splice SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-ENG2</t>
+          <t>MAP Sensor</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>MAP Sensor</t>
+          <t>via SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-ENG2</t>
+          <t>MAP</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>MAP</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG2</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_a_c44 at DRB102-CABIN 18, to BUS-GNDOUT-A 6</t>
         </is>
       </c>
+      <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9641,69 +9240,64 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>in kit 354404</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>in kit 354404</t>
+          <t>solder splice SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG2</t>
+          <t>Oil Pressure Sensor</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Oil Pressure Sensor</t>
+          <t>via SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG2</t>
+          <t>OILP</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>OILP</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_b_c19 at DRB102-CABIN 29, to BUS-GNDOUT-B 7</t>
         </is>
       </c>
+      <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9753,69 +9347,64 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow-Blue</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>1191</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>8100-0461</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>solder splice SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG</t>
+          <t>Oil Temp Sensor</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Oil Temp Sensor</t>
+          <t>via SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
+          <t>OILT</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>OILT</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_b_c19 at DRB102-CABIN 29, to BUS-GNDOUT-B 7</t>
         </is>
       </c>
+      <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9865,65 +9454,60 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
           <t>M22759/16-20-5</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>solder splice SP-CANH-LAM</t>
+        </is>
+      </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>solder splice SP-CANH-LAM</t>
+          <t>r_term_end</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>r_term_end</t>
+          <t>via SP-CANH-LAM</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>via SP-CANH-LAM</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-CANH-LAM</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>SP-CANH-LAM</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin wc_h_bh_bc at DRB102-CABIN 79, to splice SP-CANH</t>
         </is>
       </c>
+      <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>Splice and 120R terminator sit in the heat-shrink right behind the CAN-Lambda plug; the shielded pair runs to it (Dan 2026-10-27; the Link CAN-Lambda has no internal terminator, manual 4.1)</t>
         </is>
@@ -9977,65 +9561,60 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
           <t>M22759/16-20-5</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>solder splice SP-CANL-LAM</t>
+        </is>
+      </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>solder splice SP-CANL-LAM</t>
+          <t>r_term_end</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>r_term_end</t>
+          <t>via SP-CANL-LAM</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>via SP-CANL-LAM</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-CANL-LAM</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>SP-CANL-LAM</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin wc_l_bh_bc at DRB102-CABIN 80, to splice SP-CANL</t>
         </is>
       </c>
+      <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>Splice and 120R terminator sit in the heat-shrink right behind the CAN-Lambda plug; the shielded pair runs to it (Dan 2026-10-27; the Link CAN-Lambda has no internal terminator, manual 4.1)</t>
         </is>
@@ -10089,77 +9668,72 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Yellow-White-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>484</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-VSS</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>CAB-VSS</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>solder splice SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG3</t>
+          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
+          <t>via SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG3</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG3</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_b_c21 at DRB102-CABIN 15, to BUS-GNDOUT-B 8</t>
         </is>
       </c>
+      <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10205,77 +9779,72 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Yellow-White-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-VSS</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>CAB-VSS</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
+          <t>ST185-AB-engine</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
           <t>VSS</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>VSS</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_vss_sig_c at DRB102-CABIN 68, to ECU-B 29</t>
         </is>
       </c>
+      <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
-      <c r="Z86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10325,77 +9894,72 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>957</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-LAMCAN-BE</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>CAB-LAMCAN-BE</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>55A1821-20-9/5-9</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>CAN H join - bulkhead, Lambda, 120 ohm end</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>CAN H join - bulkhead, Lambda, 120 ohm end</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-CANH-LAM</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>SP-CANH-LAM</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin wc_h_bh_bc at DRB102-CABIN 79, to splice SP-CANH</t>
         </is>
       </c>
+      <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>owner TBD: a half has no length estimate (drawn today as wc_h_lam_be on ECU-engine, 240 mm; wc_h_lam on CAN, ? mm)</t>
         </is>
@@ -10449,77 +10013,72 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>957</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>(cable core)</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>(cable core)</t>
+          <t>CAB-LAMCAN-BE</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>CAB-LAMCAN-BE</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>55A1821-20-9/5-9</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>CAN L join - bulkhead, Lambda, 120 ohm end</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>CAN L join - bulkhead, Lambda, 120 ohm end</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-CANL-LAM</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>SP-CANL-LAM</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin wc_l_bh_bc at DRB102-CABIN 80, to splice SP-CANL</t>
         </is>
       </c>
+      <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>owner TBD: a half has no length estimate (drawn today as wc_l_lam_be on ECU-engine, 240 mm; wc_l_lam on CAN, ? mm)</t>
         </is>
@@ -10573,69 +10132,64 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Blue-White-Yellow-Yellow</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>998</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>998</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
           <t>M22759/16-14-0</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-210-1231</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>0462-210-1231</t>
+          <t>Coil ground splice - ignition coils 1-4 to bulkhead pin 4 (POWER box NEG bar)</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Coil ground splice - ignition coils 1-4 to bulkhead pin 4 (POWER box NEG bar)</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>COPG</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>COPG</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
+      <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>Dan 2026-10-29: coil ground straight to the glove-box POWER box NEG bar (cleanest return), not the engine block stud; 14 AWG like the COP feed (w_cop_pwr_e_ae, size-12 cavity 1) and the cabin half (Dan 2026-10-30, N74 A); size-12 contact 12-14 AWG</t>
         </is>
@@ -10689,69 +10243,64 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Blue-White-Yellow</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>998</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>998</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
           <t>M22759/16-14-2</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-210-1231</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>0462-210-1231</t>
+          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 10A) to coils 1-4</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 10A) to coils 1-4</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
+      <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>Coil +12 V feed | Coil +12 V feed | 14 AWG like the cabin half (Dan 2026-10-30, N74 A): coils fire one at a time, ~8 A peak / ~4 A RMS for all 4 (Haltech 8 A per coil); COP fuse 10 A, capped by the 16 AWG branches (coil contact max 16 AWG)</t>
         </is>
@@ -10805,69 +10354,64 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Blue-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>704</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>Sensor return splice - BH-B pin 29 (ECU B22) to oil and coolant pressure</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-B pin 29 (ECU B22) to oil and coolant pressure</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>GNDOUT</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>GNDOUT</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_b_c19 at DRB102-CABIN 29, to BUS-GNDOUT-B 7</t>
         </is>
       </c>
+      <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
-      <c r="Z91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10917,26 +10461,26 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Blue-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>solder splice</t>
@@ -10944,38 +10488,33 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>Sensor return splice - BH-B pin 29 (ECU B22) to oil and coolant pressure</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-B pin 29 (ECU B22) to oil and coolant pressure</t>
+          <t>Sensor return splice - oil temp and charge temp, tied to the BH-B pin 29 splice</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Sensor return splice - oil temp and charge temp, tied to the BH-B pin 29 splice</t>
+          <t>GNDOUT</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>GNDOUT</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
           <t>SP-GNDOUT-B-ENG2 / SP-GNDOUT-B-ENG</t>
         </is>
       </c>
+      <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr"/>
       <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11025,69 +10564,64 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Blue-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>894</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>Sensor return splice - BH-B pin 15 (ECU B22) to fuel pressure and gearbox speed</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-B pin 15 (ECU B22) to fuel pressure and gearbox speed</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>GNDOUT</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>GNDOUT</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG3</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_b_c21 at DRB102-CABIN 15, to BUS-GNDOUT-B 8</t>
         </is>
       </c>
+      <c r="W93" t="inlineStr"/>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11137,69 +10671,64 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Blue-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>894</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>Sensor return splice - BH-A pin 34 (ECU A24) to coolant temp, intake temp, throttle</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-A pin 34 (ECU A24) to coolant temp, intake temp, throttle</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>GNDOUT</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>GNDOUT</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rail_sp_gndout_c at DRB102-CABIN 34, to BUS-GNDOUT-A 2</t>
         </is>
       </c>
+      <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
-      <c r="Z94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11249,69 +10778,64 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Blue-Yellow</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
           <t>M22759/16-20-6</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>Sensor return splice - BH-A pin 18 (ECU A24) to MAP and flex sensor</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-A pin 18 (ECU A24) to MAP and flex sensor</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>GNDOUT</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>GNDOUT</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG2</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_gnd_a_c44 at DRB102-CABIN 18, to BUS-GNDOUT-A 6</t>
         </is>
       </c>
+      <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11361,69 +10885,64 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Blue-White-Blue</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>780</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>780</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
           <t>M22759/16-14-2</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-210-1231</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>0462-210-1231</t>
+          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 7.5A) to injectors 1-4</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 7.5A) to injectors 1-4</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-INJ-ENG</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>SP-INJ-ENG</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
+      <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
-      <c r="Z96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>Injector +12 V feed | Injector +12 V feed | 14 AWG like the cabin half (Dan 2026-10-30, N75 A): 4 x ~1.2 A (12 ohm high-impedance), INJ fuse 7.5 A</t>
         </is>
@@ -11477,69 +10996,64 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Blue-White-White</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>957</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
           <t>M22759/16-12-2</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-210-1231</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>0462-210-1231</t>
+          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 16 AWG lead</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-LAM12-B</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>SP-LAM12-B</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
           <t>ST185-CabinPower w_lam12_cp at DRB102-CABIN 95, to LOGIC BUS2-1</t>
         </is>
       </c>
+      <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr"/>
-      <c r="Z97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>CAN-Lambda +12 V | CAN-Lambda +12 V</t>
         </is>
@@ -11593,69 +11107,64 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Blue-White-White</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>957</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
           <t>M22759/16-12-0</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-210-1231</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>0462-210-1231</t>
+          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 16 AWG lead</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-LAMG-B</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>SP-LAMG-B</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_lamg_ac at DRB102-CABIN 96, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
+      <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
-      <c r="Z98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11705,76 +11214,71 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>894</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
           <t>M22759/16-18-2</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>Switched +12 V splice - BH-A pin 30 to boost solenoid and flex sensor</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Switched +12 V splice - BH-A pin 30 to boost solenoid and flex sensor</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>ST185-AB-engine</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>ST185-AB-engine</t>
+          <t>SP-SW12-ENG</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>SP-SW12-ENG</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
           <t>ST185-AB-cabin w_rail_sp_sw12_c at DRB102-CABIN 30, to splice SP-SW12</t>
         </is>
       </c>
+      <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>+12 V boost + flex | +12 V boost + flex</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z99"/>
+  <autoFilter ref="A1:Y99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15157,7 +14661,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Colour = insulation colour (harness.design colour names). Ident bands = printed MIL-STD-681 band code.</t>
+          <t>Colour = insulation colour (harness.design colour names). No ident bands (Dan 2026-10-31).</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Y$99</definedName>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -4676,7 +4676,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>w_vss_12v</t>
+          <t>w_vss_8v</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
+          <t>+8 V to gearbox speed sensor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -4772,19 +4772,19 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_rail_sw12_b_c_ac at DRB102-CABIN 67, to splice SP-SW12</t>
+          <t>ST185-AB-cabin w_rail_sp_8v_vss_c at DRB102-CABIN 67, to splice SP-8V</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>+12 V gearbox speed | +12 V gearbox speed</t>
+          <t>Dan 2026-11-01: VSS on ECU +8V; core colour set by cable CAB-VSS</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Y$99</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Y$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Splices'!$A$1:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y99"/>
+  <dimension ref="A1:Y98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4702,7 +4702,7 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4727,19 +4727,11 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>CAB-VSS</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
+          <t>M22759/16-20-3</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>0462-201-1631</t>
@@ -4784,14 +4776,14 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Dan 2026-11-01: VSS on ECU +8V; core colour set by cable CAB-VSS</t>
+          <t>Dan 2026-11-01: VSS on ECU +8V, plain wires, no shield</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cab_vss_sh</t>
+          <t>w201_e</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4801,62 +4793,62 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NC, floats</t>
+          <t>ECT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>drain</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Gearbox speed shield</t>
+          <t>Coolant temp signal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>CAB-VSS</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
+          <t>M22759/16-20-9</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>8100-0461</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>BULKHEAD</t>
@@ -4864,12 +4856,12 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>cab_vss screen (floats at the device end)</t>
+          <t>ECT Sensor</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>ECT</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4879,26 +4871,22 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>ECT</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_shc_vss at DRB102-CABIN 69, to splice SP-SHIELD-B</t>
+          <t>ST185-AB-cabin w201_c at DRB102-CABIN 70, to ECU-A 15</t>
         </is>
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
-        </is>
-      </c>
+      <c r="Y41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>w201_e</t>
+          <t>cab_knock1_c1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4908,12 +4896,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ECT</t>
+          <t>KNOCK-1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4924,17 +4912,17 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Coolant temp signal</t>
+          <t>Knock sensor signal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4944,16 +4932,24 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>851</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>CAB-KNOCK1</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>55A1821-20-6/9-9</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>0462-201-1631</t>
@@ -4961,7 +4957,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>BDK 2.8</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4971,12 +4967,12 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>ECT Sensor</t>
+          <t>Knock Sensor 1</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>ECT</t>
+          <t>KNOCK1</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -4986,22 +4982,26 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>ECT</t>
+          <t>KNOCK1</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w201_c at DRB102-CABIN 70, to ECU-A 15</t>
+          <t>ST185-AB-cabin w205_c at DRB102-CABIN 71, to ECU-B 9</t>
         </is>
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Knock plug contacts: Bosch BDK 2.8 with individual wire seals (Bosch Compact 1.1a catalog, 1 928 403 874; Dan 2026-10-29)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cab_knock1_c1</t>
+          <t>cab_knock1_c2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -5032,12 +5032,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Knock sensor signal</t>
+          <t>Knock sensor (-)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w205_c at DRB102-CABIN 71, to ECU-B 9</t>
+          <t>ST185-AB-cabin w12_c at DRB102-CABIN 72, to BUS-GNDOUT-B 6</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
@@ -5116,7 +5116,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cab_knock1_c2</t>
+          <t>cab_knock1_sh</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5126,40 +5126,36 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KNOCK-1</t>
+          <t>NC, floats</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>drain</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Knock sensor (-)</t>
+          <t>Knock sensor shield</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>851</t>
@@ -5185,11 +5181,7 @@
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>BDK 2.8</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
           <t>BULKHEAD</t>
@@ -5197,7 +5189,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Knock Sensor 1</t>
+          <t>cab_knock1 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5217,21 +5209,21 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w12_c at DRB102-CABIN 72, to BUS-GNDOUT-B 6</t>
+          <t>ST185-AB-cabin w_shc_knock1 at DRB102-CABIN 73, to splice SP-SHIELD-B</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>Knock plug contacts: Bosch BDK 2.8 with individual wire seals (Bosch Compact 1.1a catalog, 1 928 403 874; Dan 2026-10-29)</t>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cab_knock1_sh</t>
+          <t>cab_crank_c1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5241,39 +5233,43 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NC, floats</t>
+          <t>CRANK</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>drain</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Knock sensor shield</t>
+          <t>Crank sensor signal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5283,7 +5279,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>CAB-KNOCK1</t>
+          <t>CAB-CRANK</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5296,7 +5292,11 @@
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>in kit CONN-75800</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>BULKHEAD</t>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>cab_knock1 screen (floats at the device end)</t>
+          <t>Crank VR Sensor (36-2)</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>KNOCK1</t>
+          <t>CRANK</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -5319,26 +5319,26 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>KNOCK1</t>
+          <t>CRANK</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_shc_knock1 at DRB102-CABIN 73, to splice SP-SHIELD-B</t>
+          <t>ST185-AB-cabin w200_c at DRB102-CABIN 74, to ECU-A 8</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
+          <t>Crank plug: Toyota 90980-10947 (Sumitomo 2-way TS, Ballenger kit CONN-75800, owned; Dan 2026-10-31) mates the sensor's own socket; which cavity is signal vs ground is TBD (EWD)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cab_crank_c1</t>
+          <t>w2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Crank sensor signal</t>
+          <t>Gnd crank sensor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w200_c at DRB102-CABIN 74, to ECU-A 8</t>
+          <t>ST185-AB-cabin w_gnd_a_c41 at DRB102-CABIN 75, to BUS-GNDOUT-A 3</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
@@ -5453,7 +5453,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>w2</t>
+          <t>cab_crank_sh</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5463,40 +5463,36 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRANK</t>
+          <t>NC, floats</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>drain</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Gnd crank sensor</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>1210</t>
@@ -5522,11 +5518,7 @@
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>in kit CONN-75800</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
           <t>BULKHEAD</t>
@@ -5534,7 +5526,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Crank VR Sensor (36-2)</t>
+          <t>cab_crank screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5554,21 +5546,21 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_gnd_a_c41 at DRB102-CABIN 75, to BUS-GNDOUT-A 3</t>
+          <t>ST185-AB-cabin w_shc_crank at DRB102-CABIN 76, to splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Crank plug: Toyota 90980-10947 (Sumitomo 2-way TS, Ballenger kit CONN-75800, owned; Dan 2026-10-31) mates the sensor's own socket; which cavity is signal vs ground is TBD (EWD)</t>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cab_crank_sh</t>
+          <t>w_rev_feed_e</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5578,62 +5570,62 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NC, floats</t>
+          <t>REV-SW</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>drain</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>Back-up sw +12 V in</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>CAB-CRANK</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>55A1821-20-6/9-9</t>
-        </is>
-      </c>
+          <t>M22759/16-16-2</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>8100-0461</t>
+        </is>
+      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>BULKHEAD</t>
@@ -5641,12 +5633,12 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>cab_crank screen (floats at the device end)</t>
+          <t>Back-up SW B1</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>CRANK</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -5656,26 +5648,26 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>CRANK</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_shc_crank at DRB102-CABIN 76, to splice SP-SHIELD-A</t>
+          <t>ST185-AB-cabin w_rev_feed_c at DRB102-CABIN 77, to IG2 4</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end</t>
+          <t>Housing 90980-11250 = 2.3 II mm female 2-way sealed (Toyota RM1022E housing list); plug kit owned (Ballenger BM-985510).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>w_rev_feed_e</t>
+          <t>w_sw7_e</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5685,7 +5677,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5695,7 +5687,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -5706,12 +5698,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in</t>
+          <t>Reverse sw +12 V out</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5726,7 +5718,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -5768,7 +5760,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_rev_feed_c at DRB102-CABIN 77, to IG2 4</t>
+          <t>ST185-AB-cabin w_rev_sw_c at DRB102-CABIN 78, to splice SP-REV</t>
         </is>
       </c>
       <c r="W49" t="inlineStr"/>
@@ -5782,7 +5774,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>w_sw7_e</t>
+          <t>cab_lamcan_be_sh</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5792,62 +5784,62 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>REV-SW</t>
+          <t>NC, floats</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>drain</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out</t>
+          <t>CAN-Lambda shield</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>957</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>CAB-LAMCAN-BE</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>55A1821-20-9/5-9</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>8100-0461</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
           <t>BULKHEAD</t>
@@ -5855,12 +5847,12 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Back-up SW B1</t>
+          <t>cab_can_lam screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5870,26 +5862,26 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_rev_sw_c at DRB102-CABIN 78, to splice SP-REV</t>
+          <t>ST185-AB-cabin cab_canbh_bc_sh at DRB102-CABIN 81, to splice SP-CAN-SH-BH</t>
         </is>
       </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>Housing 90980-11250 = 2.3 II mm female 2-way sealed (Toyota RM1022E housing list); plug kit owned (Ballenger BM-985510).</t>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the CAN-Lambda end; owned by AB-engine (Dan 2026-10-27)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cab_lamcan_be_sh</t>
+          <t>w_hv_mrs_en_e</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5899,62 +5891,62 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NC, floats</t>
+          <t>MRS-C</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>drain</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CAN-Lambda shield</t>
+          <t>EFI relay k_efi -&gt; LOGIC MRS 5 A fuse</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>855</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>CAB-LAMCAN-BE</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>55A1821-20-9/5-9</t>
-        </is>
-      </c>
+          <t>M22759/16-20-2</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>0462-201-1631</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>82998-12440</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>BULKHEAD</t>
@@ -5962,12 +5954,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>cab_can_lam screen (floats at the device end)</t>
+          <t>MR-S EHPS pump plug C</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -5977,26 +5969,26 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin cab_canbh_bc_sh at DRB102-CABIN 81, to splice SP-CAN-SH-BH</t>
+          <t>ST185-AB-cabin w_fb_mrs_en at DRB102-CABIN 83, to LOGIC BUS2-12</t>
         </is>
       </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the CAN-Lambda end; owned by AB-engine (Dan 2026-10-27)</t>
+          <t>EHPS enable +12 V | EHPS enable +12 V Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); lead 2.0 mm2 (about 14 AWG, Toyota RM06H0E section F), larger than the harness wire, which solder-splices to it. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>w_hv_mrs_en_e</t>
+          <t>w_mrs_e</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6006,17 +5998,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MRS-C</t>
+          <t>MRS-B</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -6027,12 +6019,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC MRS 5 A fuse</t>
+          <t>EHPS pump speed</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6047,7 +6039,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -6069,12 +6061,12 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>MR-S EHPS pump plug C</t>
+          <t>MR-S EHPS pump plug B</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>EPSEN</t>
+          <t>MRS</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -6084,26 +6076,26 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>EPSEN</t>
+          <t>MRS</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_fb_mrs_en at DRB102-CABIN 83, to LOGIC BUS2-12</t>
+          <t>ST185-AB-cabin w_mrs_c at DRB102-CABIN 84, to ECU-A 27</t>
         </is>
       </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V | EHPS enable +12 V Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); lead 2.0 mm2 (about 14 AWG, Toyota RM06H0E section F), larger than the harness wire, which solder-splices to it. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
+          <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); lead 2.0 mm2 (about 14 AWG, Toyota RM06H0E section F), larger than the harness wire, which solder-splices to it. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>w_mrs_e</t>
+          <t>w_eps_rly_e</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6113,7 +6105,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6123,7 +6115,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -6134,7 +6126,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>EHPS pump speed</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6144,7 +6136,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -6154,7 +6146,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -6181,7 +6173,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>MRS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6191,12 +6183,12 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>MRS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_mrs_c at DRB102-CABIN 84, to ECU-A 27</t>
+          <t>ST185-AB-cabin w_eps_rly at DRB102-CABIN 85, to K-EPS 85</t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
@@ -6210,85 +6202,89 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>w_eps_rly_e</t>
+          <t>w219</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>BOOST-SOL</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>DRB102-ENGINE</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>MRS-B</t>
-        </is>
-      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SP-SW12-ENG</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>262</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-20-2</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>12084200</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>82998-12440</t>
+          <t>solder splice SP-SW12-ENG</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Boost Control Solenoid</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>MR-S EHPS pump plug B</t>
+          <t>via SP-SW12-ENG</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -6298,31 +6294,31 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>SP-SW12-ENG</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_eps_rly at DRB102-CABIN 85, to K-EPS 85</t>
+          <t>ST185-AB-cabin w_rail_sp_sw12_c at DRB102-CABIN 30, to splice SP-SW12</t>
         </is>
       </c>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Contact: Toyota repair wire 82998-12440 (2.3 II mm sealed female + seal + about 6 in lead, owned; Toyota RM1022E lists it for 90980-10897 / -10942; DIYElectricCar MR2 EHPS thread); lead 2.0 mm2 (about 14 AWG, Toyota RM06H0E section F), larger than the harness wire, which solder-splices to it. | ECU engine harness owns it: leaves the bulkhead in the engine loom to the MR-S pump plug (Dan 2026-10-29); harness C keeps the 8 AWG pump power and ground</t>
+          <t>+12 V boost sol | +12 V boost sol</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>w219</t>
+          <t>w_lam12_be</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BOOST-SOL</t>
+          <t>CAN-LAMBDA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6337,12 +6333,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SP-SW12-ENG</t>
+          <t>SP-LAM12-B</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6352,7 +6348,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6362,44 +6358,44 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>12084200</t>
+          <t>0462-005-2031</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>solder splice SP-SW12-ENG</t>
+          <t>solder splice SP-LAM12-B</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Boost Control Solenoid</t>
+          <t>Link CAN-Lambda</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>via SP-SW12-ENG</t>
+          <t>via SP-LAM12-B</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6409,26 +6405,26 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SP-SW12-ENG</t>
+          <t>SP-LAM12-B</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_rail_sp_sw12_c at DRB102-CABIN 30, to splice SP-SW12</t>
+          <t>ST185-CabinPower w_lam12_cp at DRB102-CABIN 95, to LOGIC BUS2-1</t>
         </is>
       </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>+12 V boost sol | +12 V boost sol</t>
+          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner TBD: a half has no length estimate (drawn today as w_lam12_be on ECU-engine, ? mm; w_lam12_can on CAN, 140 mm)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>w_lam12_be</t>
+          <t>w_lamg_be</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6438,7 +6434,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6448,12 +6444,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SP-LAM12-B</t>
+          <t>SP-LAMG-B</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6463,12 +6459,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
+          <t>CAN-Lambda ground</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6483,7 +6479,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -6495,7 +6491,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>solder splice SP-LAM12-B</t>
+          <t>solder splice SP-LAMG-B</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -6505,7 +6501,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>via SP-LAM12-B</t>
+          <t>via SP-LAMG-B</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6520,26 +6516,26 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SP-LAM12-B</t>
+          <t>SP-LAMG-B</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_lam12_cp at DRB102-CABIN 95, to LOGIC BUS2-1</t>
+          <t>ST185-AB-cabin w_lamg_ac at DRB102-CABIN 96, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner TBD: a half has no length estimate (drawn today as w_lam12_be on ECU-engine, ? mm; w_lam12_can on CAN, 140 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_lamg_can on CAN, 140 mm; w_lamg_be on ECU-engine, ? mm)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>w_lamg_be</t>
+          <t>wc_l_lam_pin</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6549,7 +6545,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6559,12 +6555,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SP-LAMG-B</t>
+          <t>SP-CANL-LAM</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6574,39 +6570,39 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground</t>
+          <t>CAN L to CAN-Lambda</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-20-5</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0462-005-2031</t>
+          <t>0462-201-2031</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>solder splice SP-LAMG-B</t>
+          <t>solder splice SP-CANL-LAM</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -6616,12 +6612,12 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>via SP-LAMG-B</t>
+          <t>via SP-CANL-LAM</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -6631,26 +6627,26 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SP-LAMG-B</t>
+          <t>SP-CANL-LAM</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_lamg_ac at DRB102-CABIN 96, to POWER-NEG-BAR Lug</t>
+          <t>ST185-AB-cabin wc_l_bh_bc at DRB102-CABIN 80, to splice SP-CANL</t>
         </is>
       </c>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_lamg_can on CAN, 140 mm; w_lamg_be on ECU-engine, ? mm)</t>
+          <t>Splice and 120R terminator sit in the heat-shrink right behind the CAN-Lambda plug; the shielded pair runs to it (Dan 2026-10-27; the Link CAN-Lambda has no internal terminator, manual 4.1)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>wc_l_lam_pin</t>
+          <t>wc_h_lam_pin</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6660,7 +6656,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6670,12 +6666,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SP-CANL-LAM</t>
+          <t>SP-CANH-LAM</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6685,12 +6681,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CAN L to CAN-Lambda</t>
+          <t>CAN H to CAN-Lambda</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6705,7 +6701,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>M22759/16-20-5</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -6717,7 +6713,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>solder splice SP-CANL-LAM</t>
+          <t>solder splice SP-CANH-LAM</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -6727,7 +6723,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>via SP-CANL-LAM</t>
+          <t>via SP-CANH-LAM</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6742,12 +6738,12 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SP-CANL-LAM</t>
+          <t>SP-CANH-LAM</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin wc_l_bh_bc at DRB102-CABIN 80, to splice SP-CANL</t>
+          <t>ST185-AB-cabin wc_h_bh_bc at DRB102-CABIN 79, to splice SP-CANH</t>
         </is>
       </c>
       <c r="W58" t="inlineStr"/>
@@ -6761,17 +6757,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>wc_h_lam_pin</t>
+          <t>w10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CAN-LAMBDA</t>
+          <t>CHARGE-IAT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6781,12 +6777,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SP-CANH-LAM</t>
+          <t>SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6796,12 +6792,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CAN H to CAN-Lambda</t>
+          <t>Gnd charge temp</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6811,39 +6807,39 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>0462-201-2031</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>solder splice SP-CANH-LAM</t>
+          <t>solder splice SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Link CAN-Lambda</t>
+          <t>Charge-Pipe IAT Sensor</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>via SP-CANH-LAM</t>
+          <t>via SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CPIAT</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -6853,36 +6849,32 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SP-CANH-LAM</t>
+          <t>SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin wc_h_bh_bc at DRB102-CABIN 79, to splice SP-CANH</t>
+          <t>ST185-AB-cabin w_gnd_b_c19 at DRB102-CABIN 29, to BUS-GNDOUT-B 7</t>
         </is>
       </c>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>Splice and 120R terminator sit in the heat-shrink right behind the CAN-Lambda plug; the shielded pair runs to it (Dan 2026-10-27; the Link CAN-Lambda has no internal terminator, manual 4.1)</t>
-        </is>
-      </c>
+      <c r="Y59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>w10</t>
+          <t>w36</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CHARGE-IAT</t>
+          <t>CLNT-P</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6897,7 +6889,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
+          <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6907,7 +6899,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Gnd charge temp</t>
+          <t>Gnd coolant press</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6922,7 +6914,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6934,27 +6926,27 @@
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>solder splice onto the pigtail black lead</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG</t>
+          <t>solder splice SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Charge-Pipe IAT Sensor</t>
+          <t>Coolant Pressure Sensor</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
+          <t>via SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>CPIAT</t>
+          <t>CLNTP</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -6964,7 +6956,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG</t>
+          <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6979,17 +6971,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>w36</t>
+          <t>w112</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CLNT-P</t>
+          <t>COIL-1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6999,12 +6991,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -7014,54 +7006,54 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Gnd coolant press</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>293</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>solder splice onto the pigtail black lead</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG2</t>
+          <t>solder splice SP-COP-ENG</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Coolant Pressure Sensor</t>
+          <t>COP 1 (1ZZ)</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG2</t>
+          <t>via SP-COP-ENG</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>CLNTP</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -7071,22 +7063,26 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_gnd_b_c19 at DRB102-CABIN 29, to BUS-GNDOUT-B 7</t>
+          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Coil 1 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 1 +12 V</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>w112</t>
+          <t>w_cop1g</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7096,7 +7092,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7106,12 +7102,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -7121,12 +7117,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
+          <t>Coil 1 ground</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7141,7 +7137,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
@@ -7153,7 +7149,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>solder splice SP-COP-ENG</t>
+          <t>solder splice SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -7163,12 +7159,12 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>via SP-COP-ENG</t>
+          <t>via SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>COP1</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -7178,36 +7174,36 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>Coil 1 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 1 +12 V</t>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>w_cop1g</t>
+          <t>w113</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>COIL-1</t>
+          <t>COIL-2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7217,12 +7213,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7232,12 +7228,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Coil 1 ground</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7247,12 +7243,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>360</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -7264,22 +7260,22 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>solder splice SP-CHASSIS-ENG</t>
+          <t>solder splice SP-COP-ENG</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>COP 1 (1ZZ)</t>
+          <t>COP 2 (1ZZ)</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>via SP-CHASSIS-ENG</t>
+          <t>via SP-COP-ENG</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>COP1</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -7289,26 +7285,26 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+          <t>Coil 2 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 2 +12 V</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>w113</t>
+          <t>w_cop2g</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7318,7 +7314,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7328,12 +7324,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -7343,12 +7339,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
+          <t>Coil 2 ground</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7363,7 +7359,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -7375,7 +7371,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>solder splice SP-COP-ENG</t>
+          <t>solder splice SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -7385,12 +7381,12 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>via SP-COP-ENG</t>
+          <t>via SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>COP2</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -7400,36 +7396,36 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>Coil 2 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 2 +12 V</t>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>w_cop2g</t>
+          <t>w114</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>COIL-2</t>
+          <t>COIL-3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7439,12 +7435,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -7454,12 +7450,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Coil 2 ground</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7469,12 +7465,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>257</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -7486,22 +7482,22 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>solder splice SP-CHASSIS-ENG</t>
+          <t>solder splice SP-COP-ENG</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>COP 2 (1ZZ)</t>
+          <t>COP 3 (1ZZ)</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>via SP-CHASSIS-ENG</t>
+          <t>via SP-COP-ENG</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>COP2</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -7511,26 +7507,26 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+          <t>Coil 3 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 3 +12 V</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>w114</t>
+          <t>w_cop3g</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7540,7 +7536,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7550,12 +7546,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -7565,12 +7561,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
+          <t>Coil 3 ground</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7585,7 +7581,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -7597,7 +7593,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>solder splice SP-COP-ENG</t>
+          <t>solder splice SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -7607,12 +7603,12 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>via SP-COP-ENG</t>
+          <t>via SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>COP3</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -7622,36 +7618,36 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>Coil 3 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 3 +12 V</t>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>w_cop3g</t>
+          <t>w115</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>COIL-3</t>
+          <t>COIL-4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7661,12 +7657,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -7676,12 +7672,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Coil 3 ground</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7691,12 +7687,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>152</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -7708,22 +7704,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>solder splice SP-CHASSIS-ENG</t>
+          <t>solder splice SP-COP-ENG</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>COP 3 (1ZZ)</t>
+          <t>COP 4 (1ZZ)</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>via SP-CHASSIS-ENG</t>
+          <t>via SP-COP-ENG</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>COP3</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -7733,26 +7729,26 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
+          <t>Coil 4 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 4 +12 V</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>w115</t>
+          <t>w_cop4g</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7762,7 +7758,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7772,12 +7768,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7787,12 +7783,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
+          <t>Coil 4 ground</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7807,7 +7803,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -7819,7 +7815,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>solder splice SP-COP-ENG</t>
+          <t>solder splice SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -7829,12 +7825,12 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>via SP-COP-ENG</t>
+          <t>via SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>COP4</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -7844,36 +7840,36 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>Coil 4 +12 V Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet. | Coil 4 +12 V</t>
+          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>w_cop4g</t>
+          <t>w4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COIL-4</t>
+          <t>ECT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7883,12 +7879,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -7898,54 +7894,54 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Coil 4 ground</t>
+          <t>Gnd coolant temp</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>234</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>solder splice SP-CHASSIS-ENG</t>
+          <t>solder splice SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>COP 4 (1ZZ)</t>
+          <t>ECT Sensor</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>via SP-CHASSIS-ENG</t>
+          <t>via SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>COP4</t>
+          <t>ECT</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -7955,31 +7951,27 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+          <t>ST185-AB-cabin w_rail_sp_gndout_c at DRB102-CABIN 34, to BUS-GNDOUT-A 2</t>
         </is>
       </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Contact owned with the plug (Dan 2026-10-30), maker PN not known; RM1022E: 90980-11885 takes 2.3 II mm sealed female contacts. Coil pins (1ZZ 90919-02239): 1 +B, 2 IGF, 3 IGT, 4 GND per an MS EFI forum note; the Racer X kit PDF lists the same pins right-to-left; no Toyota EWD in the repo yet.</t>
-        </is>
-      </c>
+      <c r="Y69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>w4</t>
+          <t>w127</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ECT</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8004,17 +7996,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Gnd coolant temp</t>
+          <t>Gnd throttle sensor</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8024,19 +8016,27 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>136</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>CAB-ETBS</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>55A1841-20-2/4/5/6-9</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>in kit D 261 205 358-01</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>ECT Sensor</t>
+          <t>Bosch 74.5mm ETB</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>ECT</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -8081,17 +8081,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>w127</t>
+          <t>w217</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
+          <t>SP-SW12-ENG</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -8116,12 +8116,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Gnd throttle sensor</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>291</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -8141,37 +8141,37 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>CAB-ETBS</t>
+          <t>CAB-FLEX</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>in kit D 261 205 358-01</t>
+          <t>15326426</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-ENG</t>
+          <t>solder splice SP-SW12-ENG</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Bosch 74.5mm ETB</t>
+          <t>Flex Fuel Sensor</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-ENG</t>
+          <t>via SP-SW12-ENG</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>ETBS</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -8181,22 +8181,26 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
+          <t>SP-SW12-ENG</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_rail_sp_gndout_c at DRB102-CABIN 34, to BUS-GNDOUT-A 2</t>
+          <t>ST185-AB-cabin w_rail_sp_sw12_c at DRB102-CABIN 30, to splice SP-SW12</t>
         </is>
       </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>+12 V flex fuel | +12 V flex fuel</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>w217</t>
+          <t>w47</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8206,7 +8210,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8216,12 +8220,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SP-SW12-ENG</t>
+          <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -8231,12 +8235,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
+          <t>Gnd flex fuel</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8246,7 +8250,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>115</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -8271,7 +8275,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>solder splice SP-SW12-ENG</t>
+          <t>solder splice SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -8281,12 +8285,12 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>via SP-SW12-ENG</t>
+          <t>via SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -8296,36 +8300,32 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SP-SW12-ENG</t>
+          <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_rail_sp_sw12_c at DRB102-CABIN 30, to splice SP-SW12</t>
+          <t>ST185-AB-cabin w_gnd_a_c44 at DRB102-CABIN 18, to BUS-GNDOUT-A 6</t>
         </is>
       </c>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>+12 V flex fuel | +12 V flex fuel</t>
-        </is>
-      </c>
+      <c r="Y72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>w47</t>
+          <t>w33</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>FUEL-P</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8335,27 +8335,27 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG2</t>
+          <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Gnd flex fuel</t>
+          <t>Gnd fuel pressure</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8365,47 +8365,39 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>410</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>CAB-FLEX</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
+          <t>M22759/16-20-6</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>in kit 354404</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-ENG2</t>
+          <t>solder splice SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Flex Fuel Sensor</t>
+          <t>Fuel Pressure Sensor</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-ENG2</t>
+          <t>via SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>FUELP</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -8415,12 +8407,12 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG2</t>
+          <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_gnd_a_c44 at DRB102-CABIN 18, to BUS-GNDOUT-A 6</t>
+          <t>ST185-AB-cabin w_gnd_b_c21 at DRB102-CABIN 15, to BUS-GNDOUT-B 8</t>
         </is>
       </c>
       <c r="W73" t="inlineStr"/>
@@ -8430,17 +8422,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>w33</t>
+          <t>w6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FUEL-P</t>
+          <t>IAT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8450,12 +8442,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG3</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -8465,7 +8457,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Gnd fuel pressure</t>
+          <t>Gnd intake temp</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8480,7 +8472,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>394</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -8492,27 +8484,27 @@
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
-          <t>in kit 354404</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG3</t>
+          <t>solder splice SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Fuel Pressure Sensor</t>
+          <t>IAT Sensor (Manifold)</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG3</t>
+          <t>via SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>FUELP</t>
+          <t>IAT</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -8522,12 +8514,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG3</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_gnd_b_c21 at DRB102-CABIN 15, to BUS-GNDOUT-B 8</t>
+          <t>ST185-AB-cabin w_rail_sp_gndout_c at DRB102-CABIN 34, to BUS-GNDOUT-A 2</t>
         </is>
       </c>
       <c r="W74" t="inlineStr"/>
@@ -8537,32 +8529,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>w6</t>
+          <t>w211</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IAT</t>
+          <t>INJ-1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DRB102-ENGINE</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>DRB102-ENGINE</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
+          <t>SP-INJ-ENG</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -8572,54 +8564,54 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Gnd intake temp</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>275</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>in kit CONN-76270</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-ENG</t>
+          <t>solder splice SP-INJ-ENG</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>IAT Sensor (Manifold)</t>
+          <t>Injector 1</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-ENG</t>
+          <t>via SP-INJ-ENG</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>IAT</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8629,27 +8621,31 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
+          <t>SP-INJ-ENG</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_rail_sp_gndout_c at DRB102-CABIN 34, to BUS-GNDOUT-A 2</t>
+          <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Injector 1 +12 V | Injector 1 +12 V | Injector plugs: Ballenger CONN-76270 kits (black EV6/EV14 housing, GT 150 female 20-16 AWG, white cable seal 24-18 AWG), owned x4 (Dan 2026-10-31). Branches 18 AWG because the seal stops at 18 AWG (B12 step 2); load ~1.2 A each, INJ fuse 7.5 A.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>w211</t>
+          <t>w212</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>INJ-1</t>
+          <t>INJ-2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8694,7 +8690,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>188</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8716,7 +8712,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Injector 1</t>
+          <t>Injector 2</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -8748,19 +8744,19 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>Injector 1 +12 V | Injector 1 +12 V | Injector plugs: Ballenger CONN-76270 kits (black EV6/EV14 housing, GT 150 female 20-16 AWG, white cable seal 24-18 AWG), owned x4 (Dan 2026-10-31). Branches 18 AWG because the seal stops at 18 AWG (B12 step 2); load ~1.2 A each, INJ fuse 7.5 A.</t>
+          <t>Injector 2 +12 V | Injector 2 +12 V</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>w212</t>
+          <t>w213</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>INJ-2</t>
+          <t>INJ-3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8805,7 +8801,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>107</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8827,7 +8823,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Injector 2</t>
+          <t>Injector 3</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -8859,19 +8855,19 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>Injector 2 +12 V | Injector 2 +12 V</t>
+          <t>Injector 3 +12 V | Injector 3 +12 V</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>w213</t>
+          <t>w214</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>INJ-3</t>
+          <t>INJ-4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8916,7 +8912,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8938,7 +8934,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Injector 3</t>
+          <t>Injector 4</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -8970,19 +8966,19 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>Injector 3 +12 V | Injector 3 +12 V</t>
+          <t>Injector 4 +12 V | Injector 4 +12 V</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>w214</t>
+          <t>w27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>INJ-4</t>
+          <t>MAP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8997,12 +8993,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SP-INJ-ENG</t>
+          <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -9012,54 +9008,54 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
+          <t>Gnd MAP sensor</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>156</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
-          <t>in kit CONN-76270</t>
+          <t>in kit 354404</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>solder splice SP-INJ-ENG</t>
+          <t>solder splice SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Injector 4</t>
+          <t>MAP Sensor</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>via SP-INJ-ENG</t>
+          <t>via SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>MAP</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -9069,31 +9065,27 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SP-INJ-ENG</t>
+          <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
+          <t>ST185-AB-cabin w_gnd_a_c44 at DRB102-CABIN 18, to BUS-GNDOUT-A 6</t>
         </is>
       </c>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>Injector 4 +12 V | Injector 4 +12 V</t>
-        </is>
-      </c>
+      <c r="Y79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>w27</t>
+          <t>w30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MAP</t>
+          <t>OIL-P</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9108,12 +9100,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG2</t>
+          <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9123,7 +9115,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Gnd MAP sensor</t>
+          <t>Gnd oil pressure</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9138,7 +9130,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -9155,22 +9147,22 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-ENG2</t>
+          <t>solder splice SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>MAP Sensor</t>
+          <t>Oil Pressure Sensor</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-ENG2</t>
+          <t>via SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>MAP</t>
+          <t>OILP</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -9180,12 +9172,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG2</t>
+          <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_gnd_a_c44 at DRB102-CABIN 18, to BUS-GNDOUT-A 6</t>
+          <t>ST185-AB-cabin w_gnd_b_c19 at DRB102-CABIN 29, to BUS-GNDOUT-B 7</t>
         </is>
       </c>
       <c r="W80" t="inlineStr"/>
@@ -9195,17 +9187,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>w30</t>
+          <t>w8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OIL-P</t>
+          <t>OIL-T</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9220,7 +9212,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2</t>
+          <t>SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -9230,7 +9222,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Gnd oil pressure</t>
+          <t>Gnd oil temp</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9245,7 +9237,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -9257,27 +9249,27 @@
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>in kit 354404</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG2</t>
+          <t>solder splice SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Oil Pressure Sensor</t>
+          <t>Oil Temp Sensor</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG2</t>
+          <t>via SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>OILP</t>
+          <t>OILT</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -9287,7 +9279,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2</t>
+          <t>SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -9302,17 +9294,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>w8</t>
+          <t>wc_term3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>OIL-T</t>
+          <t>R-TERM-END</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9322,12 +9314,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
+          <t>SP-CANH-LAM</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -9337,12 +9329,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Gnd oil temp</t>
+          <t>Lambda 120R CAN H</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9352,39 +9344,35 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-20-5</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>8100-0461</t>
-        </is>
-      </c>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG</t>
+          <t>solder splice SP-CANH-LAM</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Oil Temp Sensor</t>
+          <t>r_term_end</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG &gt; SP-GNDOUT-B-ENG2</t>
+          <t>via SP-CANH-LAM</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>OILT</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -9394,22 +9382,26 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG</t>
+          <t>SP-CANH-LAM</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_gnd_b_c19 at DRB102-CABIN 29, to BUS-GNDOUT-B 7</t>
+          <t>ST185-AB-cabin wc_h_bh_bc at DRB102-CABIN 79, to splice SP-CANH</t>
         </is>
       </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Splice and 120R terminator sit in the heat-shrink right behind the CAN-Lambda plug; the shielded pair runs to it (Dan 2026-10-27; the Link CAN-Lambda has no internal terminator, manual 4.1)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>wc_term3</t>
+          <t>wc_term4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9419,7 +9411,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9429,12 +9421,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SP-CANH-LAM</t>
+          <t>SP-CANL-LAM</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -9444,7 +9436,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Lambda 120R CAN H</t>
+          <t>Lambda 120R CAN L</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9472,7 +9464,7 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>solder splice SP-CANH-LAM</t>
+          <t>solder splice SP-CANL-LAM</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -9482,7 +9474,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>via SP-CANH-LAM</t>
+          <t>via SP-CANL-LAM</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9497,12 +9489,12 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SP-CANH-LAM</t>
+          <t>SP-CANL-LAM</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin wc_h_bh_bc at DRB102-CABIN 79, to splice SP-CANH</t>
+          <t>ST185-AB-cabin wc_l_bh_bc at DRB102-CABIN 80, to splice SP-CANL</t>
         </is>
       </c>
       <c r="W83" t="inlineStr"/>
@@ -9516,12 +9508,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>wc_term4</t>
+          <t>w_vss_gnd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>R-TERM-END</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9536,12 +9528,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SP-CANL-LAM</t>
+          <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -9551,12 +9543,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Lambda 120R CAN L</t>
+          <t>Gnd gearbox speed</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9566,35 +9558,39 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>484</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>M22759/16-20-5</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>8100-0461</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>solder splice SP-CANL-LAM</t>
+          <t>solder splice SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>r_term_end</t>
+          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>via SP-CANL-LAM</t>
+          <t>via SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -9604,26 +9600,26 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>SP-CANL-LAM</t>
+          <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin wc_l_bh_bc at DRB102-CABIN 80, to splice SP-CANL</t>
+          <t>ST185-AB-cabin w_gnd_b_c21 at DRB102-CABIN 15, to BUS-GNDOUT-B 8</t>
         </is>
       </c>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>Splice and 120R terminator sit in the heat-shrink right behind the CAN-Lambda plug; the shielded pair runs to it (Dan 2026-10-27; the Link CAN-Lambda has no internal terminator, manual 4.1)</t>
+          <t>Dan 2026-11-01: VSS on ECU +8V, plain wires, no shield</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>w_vss_gnd</t>
+          <t>w_vss_sig_e</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9633,7 +9629,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -9643,27 +9639,23 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>SP-GNDOUT-B-ENG3</t>
-        </is>
-      </c>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Gnd gearbox speed</t>
+          <t>Gearbox speed signal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9673,24 +9665,16 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>CAB-VSS</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
+          <t>M22759/16-20-9</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>8100-0461</t>
@@ -9698,7 +9682,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>solder splice SP-GNDOUT-B-ENG3</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -9708,7 +9692,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>via SP-GNDOUT-B-ENG3</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9723,32 +9707,36 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG3</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_gnd_b_c21 at DRB102-CABIN 15, to BUS-GNDOUT-B 8</t>
+          <t>ST185-AB-cabin w_vss_sig_c at DRB102-CABIN 68, to ECU-B 29</t>
         </is>
       </c>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Dan 2026-11-01: VSS on ECU +8V, plain wires, no shield</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>w_vss_sig_e</t>
+          <t>wc_h_lam_be</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>legs of SP-CANH-LAM</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -9758,23 +9746,27 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SP-CANH-LAM</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>trunk core</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Gearbox speed signal</t>
+          <t>CAN H to CAN-Lambda</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9784,7 +9776,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>957</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9794,17 +9786,17 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>CAB-VSS</t>
+          <t>CAB-LAMCAN-BE</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9814,7 +9806,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Gearbox VSS (Toyota 83181-20040, 3-wire) - actual road speed, plug 90980-11143</t>
+          <t>CAN H join - bulkhead, Lambda, 120 ohm end</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -9824,7 +9816,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -9834,27 +9826,31 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>SP-CANH-LAM</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_vss_sig_c at DRB102-CABIN 68, to ECU-B 29</t>
+          <t>ST185-AB-cabin wc_h_bh_bc at DRB102-CABIN 79, to splice SP-CANH</t>
         </is>
       </c>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_h_lam_be on ECU-engine, 240 mm; wc_h_lam on CAN, ? mm)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>wc_h_lam_be</t>
+          <t>wc_l_lam_be</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>legs of SP-CANH-LAM</t>
+          <t>legs of SP-CANL-LAM</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9869,12 +9865,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SP-CANH-LAM</t>
+          <t>SP-CANL-LAM</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9884,12 +9880,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>CAN H to CAN-Lambda</t>
+          <t>CAN L to CAN-Lambda</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9929,7 +9925,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>CAN H join - bulkhead, Lambda, 120 ohm end</t>
+          <t>CAN L join - bulkhead, Lambda, 120 ohm end</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -9949,31 +9945,31 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SP-CANH-LAM</t>
+          <t>SP-CANL-LAM</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin wc_h_bh_bc at DRB102-CABIN 79, to splice SP-CANH</t>
+          <t>ST185-AB-cabin wc_l_bh_bc at DRB102-CABIN 80, to splice SP-CANL</t>
         </is>
       </c>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_h_lam_be on ECU-engine, 240 mm; wc_h_lam on CAN, ? mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_l_lam_be on ECU-engine, 240 mm; wc_l_lam on CAN, ? mm)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>wc_l_lam_be</t>
+          <t>w_cop_gnd_e_ae</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>legs of SP-CANL-LAM</t>
+          <t>legs of SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9988,54 +9984,46 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SP-CANL-LAM</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>trunk core</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>CAN L to CAN-Lambda</t>
+          <t>Coil ground to the POWER box NEG bar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>998</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>CAB-LAMCAN-BE</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>55A1821-20-9/5-9</t>
-        </is>
-      </c>
+          <t>M22759/16-14-0</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>solder splice</t>
@@ -10043,12 +10031,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>0462-210-1231</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>CAN L join - bulkhead, Lambda, 120 ohm end</t>
+          <t>Coil ground splice - ignition coils 1-4 to bulkhead pin 4 (POWER box NEG bar)</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -10058,7 +10046,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>COPG</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -10068,31 +10056,31 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SP-CANL-LAM</t>
+          <t>SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin wc_l_bh_bc at DRB102-CABIN 80, to splice SP-CANL</t>
+          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_l_lam_be on ECU-engine, 240 mm; wc_l_lam on CAN, ? mm)</t>
+          <t>Dan 2026-10-29: coil ground straight to the glove-box POWER box NEG bar (cleanest return), not the engine block stud; 14 AWG like the COP feed (w_cop_pwr_e_ae, size-12 cavity 1) and the cabin half (Dan 2026-10-30, N74 A); size-12 contact 12-14 AWG</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>w_cop_gnd_e_ae</t>
+          <t>w_cop_pwr_e_ae</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>legs of SP-CHASSIS-ENG</t>
+          <t>legs of SP-COP-ENG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10107,12 +10095,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -10122,12 +10110,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Coil ground to the POWER box NEG bar</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10142,7 +10130,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -10159,7 +10147,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Coil ground splice - ignition coils 1-4 to bulkhead pin 4 (POWER box NEG bar)</t>
+          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 10A) to coils 1-4</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -10169,7 +10157,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>COPG</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -10179,31 +10167,31 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SP-CHASSIS-ENG</t>
+          <t>SP-COP-ENG</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_cop_gnd_ac at DRB102-CABIN 4, to POWER-NEG-BAR Lug</t>
+          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>Dan 2026-10-29: coil ground straight to the glove-box POWER box NEG bar (cleanest return), not the engine block stud; 14 AWG like the COP feed (w_cop_pwr_e_ae, size-12 cavity 1) and the cabin half (Dan 2026-10-30, N74 A); size-12 contact 12-14 AWG</t>
+          <t>Coil +12 V feed | Coil +12 V feed | 14 AWG like the cabin half (Dan 2026-10-30, N74 A): coils fire one at a time, ~8 A peak / ~4 A RMS for all 4 (Haltech 8 A per coil); COP fuse 10 A, capped by the 16 AWG branches (coil contact max 16 AWG)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>w_cop_pwr_e_ae</t>
+          <t>w_gnd_b_e_c19</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>legs of SP-COP-ENG</t>
+          <t>legs of SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -10218,12 +10206,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -10233,27 +10221,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
+          <t>Gnd oil/clnt/temps</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>704</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -10265,12 +10253,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>0462-210-1231</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Coil +12 V splice - BH-A pin 1 (LOGIC COP 10A) to coils 1-4</t>
+          <t>Sensor return splice - BH-B pin 29 (ECU B22) to oil and coolant pressure</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -10280,7 +10268,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>GNDOUT</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -10290,26 +10278,22 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SP-COP-ENG</t>
+          <t>SP-GNDOUT-B-ENG2</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
+          <t>ST185-AB-cabin w_gnd_b_c19 at DRB102-CABIN 29, to BUS-GNDOUT-B 7</t>
         </is>
       </c>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Coil +12 V feed | Coil +12 V feed | 14 AWG like the cabin half (Dan 2026-10-30, N74 A): coils fire one at a time, ~8 A peak / ~4 A RMS for all 4 (Haltech 8 A per coil); COP fuse 10 A, capped by the 16 AWG branches (coil contact max 16 AWG)</t>
-        </is>
-      </c>
+      <c r="Y90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>w_gnd_b_e_c19</t>
+          <t>w_rail_gnd_b_e</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10324,27 +10308,27 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DRB102-ENGINE</t>
+          <t>legs of SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2</t>
+          <t>SP-GNDOUT-B-ENG2 &gt; SP-GNDOUT-B-ENG</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Gnd oil/clnt/temps</t>
+          <t>Gnd oil/charge temp</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10359,7 +10343,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -10376,7 +10360,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -10386,7 +10370,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>Sensor return splice - oil temp and charge temp, tied to the BH-B pin 29 splice</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10401,14 +10385,10 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>ST185-AB-cabin w_gnd_b_c19 at DRB102-CABIN 29, to BUS-GNDOUT-B 7</t>
-        </is>
-      </c>
+          <t>SP-GNDOUT-B-ENG2 / SP-GNDOUT-B-ENG</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
@@ -10416,12 +10396,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>w_rail_gnd_b_e</t>
+          <t>w_gnd_b_e_c21</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>legs of SP-GNDOUT-B-ENG2</t>
+          <t>legs of SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10431,27 +10411,27 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>legs of SP-GNDOUT-B-ENG</t>
+          <t>DRB102-ENGINE</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2 &gt; SP-GNDOUT-B-ENG</t>
+          <t>SP-GNDOUT-B-ENG3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Gnd oil/charge temp</t>
+          <t>Gnd fuel press + VSS</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10466,7 +10446,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>894</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -10483,17 +10463,17 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-B pin 29 (ECU B22) to oil and coolant pressure</t>
+          <t>Sensor return splice - BH-B pin 15 (ECU B22) to fuel pressure and gearbox speed</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Sensor return splice - oil temp and charge temp, tied to the BH-B pin 29 splice</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10508,10 +10488,14 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG2 / SP-GNDOUT-B-ENG</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr"/>
+          <t>SP-GNDOUT-B-ENG3</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin w_gnd_b_c21 at DRB102-CABIN 15, to BUS-GNDOUT-B 8</t>
+        </is>
+      </c>
       <c r="W92" t="inlineStr"/>
       <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr"/>
@@ -10519,12 +10503,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>w_gnd_b_e_c21</t>
+          <t>w_rail_sp_gndout_e</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>legs of SP-GNDOUT-B-ENG3</t>
+          <t>legs of SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10539,12 +10523,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG3</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -10554,7 +10538,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Gnd fuel press + VSS</t>
+          <t>Gnd IAT/TPS/coolant</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10591,7 +10575,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-B pin 15 (ECU B22) to fuel pressure and gearbox speed</t>
+          <t>Sensor return splice - BH-A pin 34 (ECU A24) to coolant temp, intake temp, throttle</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -10611,12 +10595,12 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-B-ENG3</t>
+          <t>SP-GNDOUT-ENG</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_gnd_b_c21 at DRB102-CABIN 15, to BUS-GNDOUT-B 8</t>
+          <t>ST185-AB-cabin w_rail_sp_gndout_c at DRB102-CABIN 34, to BUS-GNDOUT-A 2</t>
         </is>
       </c>
       <c r="W93" t="inlineStr"/>
@@ -10626,12 +10610,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>w_rail_sp_gndout_e</t>
+          <t>w_gnd_a_e_c44</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>legs of SP-GNDOUT-ENG</t>
+          <t>legs of SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10646,12 +10630,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
+          <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -10661,7 +10645,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Gnd IAT/TPS/coolant</t>
+          <t>Gnd flex + MAP</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10676,7 +10660,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -10698,7 +10682,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-A pin 34 (ECU A24) to coolant temp, intake temp, throttle</t>
+          <t>Sensor return splice - BH-A pin 18 (ECU A24) to MAP and flex sensor</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -10718,12 +10702,12 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG</t>
+          <t>SP-GNDOUT-ENG2</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_rail_sp_gndout_c at DRB102-CABIN 34, to BUS-GNDOUT-A 2</t>
+          <t>ST185-AB-cabin w_gnd_a_c44 at DRB102-CABIN 18, to BUS-GNDOUT-A 6</t>
         </is>
       </c>
       <c r="W94" t="inlineStr"/>
@@ -10733,12 +10717,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>w_gnd_a_e_c44</t>
+          <t>w_inj_pwr_e_ae</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>legs of SP-GNDOUT-ENG2</t>
+          <t>legs of SP-INJ-ENG</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10753,12 +10737,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG2</t>
+          <t>SP-INJ-ENG</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -10768,27 +10752,27 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Gnd flex + MAP</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>780</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -10800,12 +10784,12 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>0462-210-1231</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-A pin 18 (ECU A24) to MAP and flex sensor</t>
+          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 7.5A) to injectors 1-4</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -10815,7 +10799,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>GNDOUT</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -10825,27 +10809,31 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SP-GNDOUT-ENG2</t>
+          <t>SP-INJ-ENG</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_gnd_a_c44 at DRB102-CABIN 18, to BUS-GNDOUT-A 6</t>
+          <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>Injector +12 V feed | Injector +12 V feed | 14 AWG like the cabin half (Dan 2026-10-30, N75 A): 4 x ~1.2 A (12 ohm high-impedance), INJ fuse 7.5 A</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>w_inj_pwr_e_ae</t>
+          <t>w_lam12_be14</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>legs of SP-INJ-ENG</t>
+          <t>legs of SP-LAM12-B</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10860,12 +10848,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SP-INJ-ENG</t>
+          <t>SP-LAM12-B</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -10875,7 +10863,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10885,17 +10873,17 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>957</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>M22759/16-12-2</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -10912,7 +10900,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Injector +12 V splice - BH-A pin 2 (LOGIC INJ 7.5A) to injectors 1-4</t>
+          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -10922,7 +10910,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
@@ -10932,31 +10920,31 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SP-INJ-ENG</t>
+          <t>SP-LAM12-B</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
+          <t>ST185-CabinPower w_lam12_cp at DRB102-CABIN 95, to LOGIC BUS2-1</t>
         </is>
       </c>
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>Injector +12 V feed | Injector +12 V feed | 14 AWG like the cabin half (Dan 2026-10-30, N75 A): 4 x ~1.2 A (12 ohm high-impedance), INJ fuse 7.5 A</t>
+          <t>CAN-Lambda +12 V | CAN-Lambda +12 V</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>w_lam12_be14</t>
+          <t>w_lamg_be14</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>legs of SP-LAM12-B</t>
+          <t>legs of SP-LAMG-B</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10971,12 +10959,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SP-LAM12-B</t>
+          <t>SP-LAMG-B</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -10986,12 +10974,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
+          <t>CAN-Lambda ground</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11006,7 +10994,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>M22759/16-12-0</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -11023,7 +11011,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V splice - 12 AWG from BH-B pin 95 to the 16 AWG lead</t>
+          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 16 AWG lead</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -11043,31 +11031,27 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SP-LAM12-B</t>
+          <t>SP-LAMG-B</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_lam12_cp at DRB102-CABIN 95, to LOGIC BUS2-1</t>
+          <t>ST185-AB-cabin w_lamg_ac at DRB102-CABIN 96, to POWER-NEG-BAR Lug</t>
         </is>
       </c>
       <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>CAN-Lambda +12 V | CAN-Lambda +12 V</t>
-        </is>
-      </c>
+      <c r="Y97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>w_lamg_be14</t>
+          <t>w_rail_sp_sw12_e</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>legs of SP-LAMG-B</t>
+          <t>legs of SP-SW12-ENG</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -11082,12 +11066,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SP-LAMG-B</t>
+          <t>SP-SW12-ENG</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -11097,27 +11081,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>894</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -11129,12 +11113,12 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>0462-210-1231</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground splice - 12 AWG from BH-B pin 96 to the 16 AWG lead</t>
+          <t>Switched +12 V splice - BH-A pin 30 to boost solenoid and flex sensor</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -11144,7 +11128,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -11154,131 +11138,24 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SP-LAMG-B</t>
+          <t>SP-SW12-ENG</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin w_lamg_ac at DRB102-CABIN 96, to POWER-NEG-BAR Lug</t>
+          <t>ST185-AB-cabin w_rail_sp_sw12_c at DRB102-CABIN 30, to splice SP-SW12</t>
         </is>
       </c>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>w_rail_sp_sw12_e</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>legs of SP-SW12-ENG</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>DRB102-ENGINE</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>SP-SW12-ENG</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>trunk</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>M22759/16-18-2</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>solder splice</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>0462-201-1631</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>Switched +12 V splice - BH-A pin 30 to boost solenoid and flex sensor</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>SW12</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SP-SW12-ENG</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>ST185-AB-cabin w_rail_sp_sw12_c at DRB102-CABIN 30, to splice SP-SW12</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr">
+      <c r="Y98" t="inlineStr">
         <is>
           <t>+12 V boost + flex | +12 V boost + flex</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y99"/>
+  <autoFilter ref="A1:Y98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11289,7 +11166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11776,10 +11653,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -13186,35 +13063,8 @@
       </c>
       <c r="I53" t="inlineStr"/>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>CAB-VSS</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>cable screen</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>cab_vss screen (floats at the device end)</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I54"/>
+  <autoFilter ref="A1:I53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13715,7 +13565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14282,7 +14132,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -14304,7 +14154,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -14326,7 +14176,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -14348,7 +14198,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -14370,7 +14220,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -14392,7 +14242,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14414,7 +14264,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14436,7 +14286,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14458,7 +14308,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14480,7 +14330,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14502,12 +14352,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0413-214-1205</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -14524,7 +14374,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14546,7 +14396,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -14568,7 +14418,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -14590,7 +14440,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -14612,22 +14462,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0413-214-1205</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DRB102-ENGINE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>0413-214-1205</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>spare, sealing plug</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D41"/>
+  <autoFilter ref="A1:D42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14717,7 +14589,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wires: 98   Connectors / ends: 53   Splices: 13   Spare cavities: 40</t>
+          <t>Wires: 97   Connectors / ends: 52   Splices: 13   Spare cavities: 41</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -5591,7 +5591,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in</t>
+          <t>+12 V to reverse switch</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Back-up SW B1</t>
+          <t>Reverse switch (EWD back-up SW B1)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out</t>
+          <t>Switched +12 V from reverse switch</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Back-up SW B1</t>
+          <t>Reverse switch (EWD back-up SW B1)</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
+          <t>+12 V</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Gnd charge temp</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Gnd coolant press</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
+          <t>+12 V</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Coil 1 ground</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
+          <t>+12 V</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Coil 2 ground</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
+          <t>+12 V</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Coil 3 ground</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
+          <t>+12 V</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Coil 4 ground</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Gnd coolant temp</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Gnd throttle sensor</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
+          <t>+12 V</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Gnd flex fuel</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Gnd fuel pressure</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Gnd intake temp</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
+          <t>+12 V</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
+          <t>+12 V</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
+          <t>+12 V</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
+          <t>+12 V</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Gnd MAP sensor</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Gnd oil pressure</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Gnd oil temp</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Gnd gearbox speed</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Gearbox speed signal</t>
+          <t>Signal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Back-up SW B1</t>
+          <t>Reverse switch (EWD back-up SW B1)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -10221,7 +10221,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Gnd oil/clnt/temps</t>
+          <t>Gnd to oil pressure, coolant pressure, oil temp, charge temp</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Gnd oil/charge temp</t>
+          <t>Gnd to oil temp, charge temp</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Gnd fuel press + VSS</t>
+          <t>Gnd to fuel pressure, gearbox speed</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Gnd IAT/TPS/coolant</t>
+          <t>Gnd to intake temp, throttle sensor, coolant temp</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Gnd flex + MAP</t>
+          <t>Gnd to flex fuel, MAP sensor</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-engine-wirelist.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_strl_c at DRB102-CABIN 3, to RB4 4</t>
+          <t>ST185-AB-cabin w_strl_c at DRB102-CABIN 3, to RB4 4</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_lam12_cp at DRB102-CABIN 95, to LOGIC BUS2-1</t>
+          <t>ST185-AB-cabin w_lam12_cp at DRB102-CABIN 95, to LOGIC BUS2-1</t>
         </is>
       </c>
       <c r="W55" t="inlineStr"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
+          <t>ST185-AB-cabin w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
       <c r="W61" t="inlineStr"/>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
+          <t>ST185-AB-cabin w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
       <c r="W63" t="inlineStr"/>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
+          <t>ST185-AB-cabin w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
       <c r="W65" t="inlineStr"/>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
+          <t>ST185-AB-cabin w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
       <c r="W67" t="inlineStr"/>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
+          <t>ST185-AB-cabin w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
       <c r="W75" t="inlineStr"/>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
+          <t>ST185-AB-cabin w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
       <c r="W76" t="inlineStr"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
+          <t>ST185-AB-cabin w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
       <c r="W77" t="inlineStr"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
+          <t>ST185-AB-cabin w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
       <c r="W78" t="inlineStr"/>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
+          <t>ST185-AB-cabin w_cop_pwr_ac at DRB102-CABIN 1, to LOGIC BUS2-3</t>
         </is>
       </c>
       <c r="W89" t="inlineStr"/>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
+          <t>ST185-AB-cabin w_inj_pwr_ac at DRB102-CABIN 2, to LOGIC BUS2-4</t>
         </is>
       </c>
       <c r="W95" t="inlineStr"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>ST185-CabinPower w_lam12_cp at DRB102-CABIN 95, to LOGIC BUS2-1</t>
+          <t>ST185-AB-cabin w_lam12_cp at DRB102-CABIN 95, to LOGIC BUS2-1</t>
         </is>
       </c>
       <c r="W96" t="inlineStr"/>
